--- a/ProductionBuild/fullviewfinancials.result.xlsx
+++ b/ProductionBuild/fullviewfinancials.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ47"/>
+  <dimension ref="A1:AK47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -477,60 +477,65 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>totalreturn</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>totalreturnover10</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>shares500</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>totalspend</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>fiveyearequityproj</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>fiveyeardivproj</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>totalfiveyearview</t>
         </is>
@@ -610,40 +615,45 @@
       <c r="W2">
         <v>0.834</v>
       </c>
-      <c r="Y2">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z2">
         <v>1.1849</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>11.849</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>25</v>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <v>30.45000076293945</v>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>5.450000762939453</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>17.29900076293945</v>
       </c>
-      <c r="AE2">
+      <c r="AF2">
         <v>1.729900076293945</v>
       </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>17</v>
       </c>
-      <c r="AG2">
+      <c r="AH2">
         <v>517.6500129699707</v>
       </c>
-      <c r="AH2">
+      <c r="AI2">
         <v>8.649500381469727</v>
       </c>
-      <c r="AI2">
+      <c r="AJ2">
         <v>5.9245</v>
       </c>
-      <c r="AJ2">
+      <c r="AK2">
         <v>14.57400038146973</v>
       </c>
     </row>
@@ -721,40 +731,45 @@
       <c r="W3">
         <v>1.707</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z3">
         <v>1.1421</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>11.421</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>16.47999954223633</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>45.83000183105469</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>29.35000228881836</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>40.77100228881836</v>
       </c>
-      <c r="AE3">
+      <c r="AF3">
         <v>4.077100228881836</v>
       </c>
-      <c r="AF3">
+      <c r="AG3">
         <v>11</v>
       </c>
-      <c r="AG3">
+      <c r="AH3">
         <v>504.1300201416016</v>
       </c>
-      <c r="AH3">
+      <c r="AI3">
         <v>20.38550114440918</v>
       </c>
-      <c r="AI3">
+      <c r="AJ3">
         <v>5.710500000000001</v>
       </c>
-      <c r="AJ3">
+      <c r="AK3">
         <v>26.09600114440918</v>
       </c>
     </row>
@@ -832,40 +847,45 @@
       <c r="W4">
         <v>0.545</v>
       </c>
-      <c r="Y4">
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z4">
         <v>0.9964000000000001</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>9.964</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>21.84000015258789</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>26.39999961853027</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>4.559999465942383</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>14.52399946594238</v>
       </c>
-      <c r="AE4">
+      <c r="AF4">
         <v>1.452399946594238</v>
       </c>
-      <c r="AF4">
+      <c r="AG4">
         <v>19</v>
       </c>
-      <c r="AG4">
+      <c r="AH4">
         <v>501.5999927520752</v>
       </c>
-      <c r="AH4">
+      <c r="AI4">
         <v>7.261999732971192</v>
       </c>
-      <c r="AI4">
+      <c r="AJ4">
         <v>4.982</v>
       </c>
-      <c r="AJ4">
+      <c r="AK4">
         <v>12.24399973297119</v>
       </c>
     </row>
@@ -946,40 +966,45 @@
       <c r="X5">
         <v>0.48</v>
       </c>
-      <c r="Y5">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z5">
         <v>1.564545454545454</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>17.21</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>16.48999977111816</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>18.95999908447266</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>2.469999313354492</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>19.67999931335449</v>
       </c>
-      <c r="AE5">
+      <c r="AF5">
         <v>1.967999931335449</v>
       </c>
-      <c r="AF5">
+      <c r="AG5">
         <v>27</v>
       </c>
-      <c r="AG5">
+      <c r="AH5">
         <v>511.9199752807617</v>
       </c>
-      <c r="AH5">
+      <c r="AI5">
         <v>9.839999656677247</v>
       </c>
-      <c r="AI5">
+      <c r="AJ5">
         <v>7.822727272727272</v>
       </c>
-      <c r="AJ5">
+      <c r="AK5">
         <v>17.66272692940452</v>
       </c>
     </row>
@@ -1060,40 +1085,45 @@
       <c r="X6">
         <v>0.37</v>
       </c>
-      <c r="Y6">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z6">
         <v>0.9781818181818183</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>10.76</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>35.7400016784668</v>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <v>37.56000137329102</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>1.819999694824219</v>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <v>12.57999969482422</v>
       </c>
-      <c r="AE6">
+      <c r="AF6">
         <v>1.257999969482422</v>
       </c>
-      <c r="AF6">
+      <c r="AG6">
         <v>14</v>
       </c>
-      <c r="AG6">
+      <c r="AH6">
         <v>525.8400192260742</v>
       </c>
-      <c r="AH6">
+      <c r="AI6">
         <v>6.289999847412108</v>
       </c>
-      <c r="AI6">
+      <c r="AJ6">
         <v>4.890909090909092</v>
       </c>
-      <c r="AJ6">
+      <c r="AK6">
         <v>11.1809089383212</v>
       </c>
     </row>
@@ -1174,40 +1204,45 @@
       <c r="X7">
         <v>0.699</v>
       </c>
-      <c r="Y7">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z7">
         <v>0.9795454545454545</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>10.775</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>15.53947353363037</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <v>17.19000053405762</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>1.650527000427246</v>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <v>12.42552700042725</v>
       </c>
-      <c r="AE7">
+      <c r="AF7">
         <v>1.242552700042725</v>
       </c>
-      <c r="AF7">
+      <c r="AG7">
         <v>30</v>
       </c>
-      <c r="AG7">
+      <c r="AH7">
         <v>515.7000160217285</v>
       </c>
-      <c r="AH7">
+      <c r="AI7">
         <v>6.212763500213622</v>
       </c>
-      <c r="AI7">
+      <c r="AJ7">
         <v>4.897727272727272</v>
       </c>
-      <c r="AJ7">
+      <c r="AK7">
         <v>11.1104907729409</v>
       </c>
     </row>
@@ -1285,40 +1320,45 @@
       <c r="W8">
         <v>2.436</v>
       </c>
-      <c r="Y8">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z8">
         <v>1.6056</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>16.056</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>25.20000076293945</v>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <v>49.31000137329102</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>24.11000061035156</v>
       </c>
-      <c r="AD8">
+      <c r="AE8">
         <v>40.16600061035156</v>
       </c>
-      <c r="AE8">
+      <c r="AF8">
         <v>4.016600061035156</v>
       </c>
-      <c r="AF8">
+      <c r="AG8">
         <v>11</v>
       </c>
-      <c r="AG8">
+      <c r="AH8">
         <v>542.4100151062012</v>
       </c>
-      <c r="AH8">
+      <c r="AI8">
         <v>20.08300030517578</v>
       </c>
-      <c r="AI8">
+      <c r="AJ8">
         <v>8.027999999999999</v>
       </c>
-      <c r="AJ8">
+      <c r="AK8">
         <v>28.11100030517578</v>
       </c>
     </row>
@@ -1399,40 +1439,45 @@
       <c r="X9">
         <v>0.708</v>
       </c>
-      <c r="Y9">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z9">
         <v>0.4082727272727272</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>4.491</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>6.769999980926514</v>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <v>22.46999931335449</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>15.69999933242798</v>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <v>20.19099933242798</v>
       </c>
-      <c r="AE9">
+      <c r="AF9">
         <v>2.019099933242798</v>
       </c>
-      <c r="AF9">
+      <c r="AG9">
         <v>23</v>
       </c>
-      <c r="AG9">
+      <c r="AH9">
         <v>516.8099842071533</v>
       </c>
-      <c r="AH9">
+      <c r="AI9">
         <v>10.09549966621399</v>
       </c>
-      <c r="AI9">
+      <c r="AJ9">
         <v>2.041363636363636</v>
       </c>
-      <c r="AJ9">
+      <c r="AK9">
         <v>12.13686330257763</v>
       </c>
     </row>
@@ -1510,40 +1555,45 @@
       <c r="X10">
         <v>2.183</v>
       </c>
-      <c r="Y10">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z10">
         <v>1.3828666</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>13.828666</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>23.48333358764648</v>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <v>39.20000076293945</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>15.71666717529297</v>
       </c>
-      <c r="AD10">
+      <c r="AE10">
         <v>29.54533317529297</v>
       </c>
-      <c r="AE10">
+      <c r="AF10">
         <v>2.954533317529297</v>
       </c>
-      <c r="AF10">
+      <c r="AG10">
         <v>13</v>
       </c>
-      <c r="AG10">
+      <c r="AH10">
         <v>509.6000099182129</v>
       </c>
-      <c r="AH10">
+      <c r="AI10">
         <v>14.77266658764648</v>
       </c>
-      <c r="AI10">
+      <c r="AJ10">
         <v>6.914333</v>
       </c>
-      <c r="AJ10">
+      <c r="AK10">
         <v>21.68699958764648</v>
       </c>
     </row>
@@ -1624,40 +1674,45 @@
       <c r="X11">
         <v>0.33</v>
       </c>
-      <c r="Y11">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z11">
         <v>1.26</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>13.86</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>39.58000183105469</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <v>27.23999977111816</v>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>-12.34000205993652</v>
       </c>
-      <c r="AD11">
+      <c r="AE11">
         <v>1.519997940063478</v>
       </c>
-      <c r="AE11">
+      <c r="AF11">
         <v>0.1519997940063478</v>
       </c>
-      <c r="AF11">
+      <c r="AG11">
         <v>19</v>
       </c>
-      <c r="AG11">
+      <c r="AH11">
         <v>517.5599956512451</v>
       </c>
-      <c r="AH11">
+      <c r="AI11">
         <v>0.7599989700317389</v>
       </c>
-      <c r="AI11">
+      <c r="AJ11">
         <v>6.3</v>
       </c>
-      <c r="AJ11">
+      <c r="AK11">
         <v>7.059998970031739</v>
       </c>
     </row>
@@ -1732,40 +1787,45 @@
       <c r="W12">
         <v>2.708</v>
       </c>
-      <c r="Y12">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z12">
         <v>1.915888888888889</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>17.243</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>31.85000038146973</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <v>53.41999816894531</v>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <v>21.56999778747559</v>
       </c>
-      <c r="AD12">
+      <c r="AE12">
         <v>38.81299778747559</v>
       </c>
-      <c r="AE12">
+      <c r="AF12">
         <v>3.881299778747559</v>
       </c>
-      <c r="AF12">
+      <c r="AG12">
         <v>10</v>
       </c>
-      <c r="AG12">
+      <c r="AH12">
         <v>534.1999816894531</v>
       </c>
-      <c r="AH12">
+      <c r="AI12">
         <v>19.40649889373779</v>
       </c>
-      <c r="AI12">
+      <c r="AJ12">
         <v>9.579444444444444</v>
       </c>
-      <c r="AJ12">
+      <c r="AK12">
         <v>28.98594333818224</v>
       </c>
     </row>
@@ -1843,40 +1903,45 @@
       <c r="W13">
         <v>2.283</v>
       </c>
-      <c r="Y13">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z13">
         <v>2.5806</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>25.806</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>55.68000030517578</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <v>75.87000274658203</v>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <v>20.19000244140625</v>
       </c>
-      <c r="AD13">
+      <c r="AE13">
         <v>45.99600244140625</v>
       </c>
-      <c r="AE13">
+      <c r="AF13">
         <v>4.599600244140625</v>
       </c>
-      <c r="AF13">
+      <c r="AG13">
         <v>7</v>
       </c>
-      <c r="AG13">
+      <c r="AH13">
         <v>531.0900192260742</v>
       </c>
-      <c r="AH13">
+      <c r="AI13">
         <v>22.99800122070312</v>
       </c>
-      <c r="AI13">
+      <c r="AJ13">
         <v>12.903</v>
       </c>
-      <c r="AJ13">
+      <c r="AK13">
         <v>35.90100122070312</v>
       </c>
     </row>
@@ -1951,40 +2016,45 @@
       <c r="W14">
         <v>1.329</v>
       </c>
-      <c r="Y14">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z14">
         <v>1.117222222222222</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>10.055</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>21.8700008392334</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <v>34.15999984741211</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>12.28999900817871</v>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>22.34499900817871</v>
       </c>
-      <c r="AE14">
+      <c r="AF14">
         <v>2.234499900817871</v>
       </c>
-      <c r="AF14">
+      <c r="AG14">
         <v>15</v>
       </c>
-      <c r="AG14">
+      <c r="AH14">
         <v>512.3999977111816</v>
       </c>
-      <c r="AH14">
+      <c r="AI14">
         <v>11.17249950408936</v>
       </c>
-      <c r="AI14">
+      <c r="AJ14">
         <v>5.58611111111111</v>
       </c>
-      <c r="AJ14">
+      <c r="AK14">
         <v>16.75861061520047</v>
       </c>
     </row>
@@ -2035,22 +2105,27 @@
       <c r="X15">
         <v>0.77</v>
       </c>
-      <c r="Y15">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z15">
         <v>2.218333333333333</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>13.31</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>24.17000007629395</v>
       </c>
-      <c r="AF15">
+      <c r="AG15">
         <v>21</v>
       </c>
-      <c r="AG15">
+      <c r="AH15">
         <v>507.5700016021729</v>
       </c>
-      <c r="AI15">
+      <c r="AJ15">
         <v>11.09166666666667</v>
       </c>
     </row>
@@ -2131,40 +2206,45 @@
       <c r="X16">
         <v>1.218</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z16">
         <v>2.433545454545455</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>26.769</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>36.68000030517578</v>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <v>73.20999908447266</v>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <v>36.52999877929688</v>
       </c>
-      <c r="AD16">
+      <c r="AE16">
         <v>63.29899877929688</v>
       </c>
-      <c r="AE16">
+      <c r="AF16">
         <v>6.329899877929688</v>
       </c>
-      <c r="AF16">
+      <c r="AG16">
         <v>7</v>
       </c>
-      <c r="AG16">
+      <c r="AH16">
         <v>512.4699935913086</v>
       </c>
-      <c r="AH16">
+      <c r="AI16">
         <v>31.64949938964844</v>
       </c>
-      <c r="AI16">
+      <c r="AJ16">
         <v>12.16772727272727</v>
       </c>
-      <c r="AJ16">
+      <c r="AK16">
         <v>43.81722666237572</v>
       </c>
     </row>
@@ -2245,40 +2325,45 @@
       <c r="X17">
         <v>2.48</v>
       </c>
-      <c r="Y17">
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z17">
         <v>2.987272727272727</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>32.86</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>41.5</v>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <v>48.16999816894531</v>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <v>6.669998168945313</v>
       </c>
-      <c r="AD17">
+      <c r="AE17">
         <v>39.52999816894531</v>
       </c>
-      <c r="AE17">
+      <c r="AF17">
         <v>3.952999816894531</v>
       </c>
-      <c r="AF17">
+      <c r="AG17">
         <v>11</v>
       </c>
-      <c r="AG17">
+      <c r="AH17">
         <v>529.8699798583984</v>
       </c>
-      <c r="AH17">
+      <c r="AI17">
         <v>19.76499908447266</v>
       </c>
-      <c r="AI17">
+      <c r="AJ17">
         <v>14.93636363636364</v>
       </c>
-      <c r="AJ17">
+      <c r="AK17">
         <v>34.70136272083629</v>
       </c>
     </row>
@@ -2359,40 +2444,45 @@
       <c r="X18">
         <v>0.37</v>
       </c>
-      <c r="Y18">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z18">
         <v>1.171818181818182</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>12.89</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>44.68000030517578</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>29.09000015258789</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>-15.59000015258789</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>-2.70000015258789</v>
       </c>
-      <c r="AE18">
+      <c r="AF18">
         <v>-0.270000015258789</v>
       </c>
-      <c r="AF18">
+      <c r="AG18">
         <v>18</v>
       </c>
-      <c r="AG18">
+      <c r="AH18">
         <v>523.620002746582</v>
       </c>
-      <c r="AH18">
+      <c r="AI18">
         <v>-1.350000076293945</v>
       </c>
-      <c r="AI18">
+      <c r="AJ18">
         <v>5.859090909090909</v>
       </c>
-      <c r="AJ18">
+      <c r="AK18">
         <v>4.509090832796964</v>
       </c>
     </row>
@@ -2473,40 +2563,45 @@
       <c r="X19">
         <v>2.535</v>
       </c>
-      <c r="Y19">
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z19">
         <v>3.441421636363637</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>37.855638</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>43.40909194946289</v>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <v>179.1499938964844</v>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <v>135.7409019470215</v>
       </c>
-      <c r="AD19">
+      <c r="AE19">
         <v>173.5965399470215</v>
       </c>
-      <c r="AE19">
+      <c r="AF19">
         <v>17.35965399470215</v>
       </c>
-      <c r="AF19">
+      <c r="AG19">
         <v>3</v>
       </c>
-      <c r="AG19">
+      <c r="AH19">
         <v>537.4499816894531</v>
       </c>
-      <c r="AH19">
+      <c r="AI19">
         <v>86.79826997351074</v>
       </c>
-      <c r="AI19">
+      <c r="AJ19">
         <v>17.20710818181818</v>
       </c>
-      <c r="AJ19">
+      <c r="AK19">
         <v>104.0053781553289</v>
       </c>
     </row>
@@ -2584,40 +2679,45 @@
       <c r="X20">
         <v>1.765</v>
       </c>
-      <c r="Y20">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z20">
         <v>0.7968000000000001</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>7.968</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>15.18000030517578</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>25.79999923706055</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>10.61999893188477</v>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>18.58799893188477</v>
       </c>
-      <c r="AE20">
+      <c r="AF20">
         <v>1.858799893188477</v>
       </c>
-      <c r="AF20">
+      <c r="AG20">
         <v>20</v>
       </c>
-      <c r="AG20">
+      <c r="AH20">
         <v>515.9999847412109</v>
       </c>
-      <c r="AH20">
+      <c r="AI20">
         <v>9.293999465942383</v>
       </c>
-      <c r="AI20">
+      <c r="AJ20">
         <v>3.984</v>
       </c>
-      <c r="AJ20">
+      <c r="AK20">
         <v>13.27799946594238</v>
       </c>
     </row>
@@ -2698,40 +2798,45 @@
       <c r="X21">
         <v>0.52</v>
       </c>
-      <c r="Y21">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z21">
         <v>1.269100090909091</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>13.960101</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>22.73556709289551</v>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <v>50.68000030517578</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>27.94443321228027</v>
       </c>
-      <c r="AD21">
+      <c r="AE21">
         <v>41.90453421228028</v>
       </c>
-      <c r="AE21">
+      <c r="AF21">
         <v>4.190453421228027</v>
       </c>
-      <c r="AF21">
+      <c r="AG21">
         <v>10</v>
       </c>
-      <c r="AG21">
+      <c r="AH21">
         <v>506.8000030517578</v>
       </c>
-      <c r="AH21">
+      <c r="AI21">
         <v>20.95226710614014</v>
       </c>
-      <c r="AI21">
+      <c r="AJ21">
         <v>6.345500454545454</v>
       </c>
-      <c r="AJ21">
+      <c r="AK21">
         <v>27.29776756068559</v>
       </c>
     </row>
@@ -2812,40 +2917,45 @@
       <c r="X22">
         <v>0.155</v>
       </c>
-      <c r="Y22">
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z22">
         <v>0.4990909090909091</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>5.49</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>13.22000026702881</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>16.96999931335449</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>3.749999046325684</v>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>9.239999046325684</v>
       </c>
-      <c r="AE22">
+      <c r="AF22">
         <v>0.9239999046325684</v>
       </c>
-      <c r="AF22">
+      <c r="AG22">
         <v>30</v>
       </c>
-      <c r="AG22">
+      <c r="AH22">
         <v>509.0999794006348</v>
       </c>
-      <c r="AH22">
+      <c r="AI22">
         <v>4.619999523162842</v>
       </c>
-      <c r="AI22">
+      <c r="AJ22">
         <v>2.495454545454546</v>
       </c>
-      <c r="AJ22">
+      <c r="AK22">
         <v>7.115454068617387</v>
       </c>
     </row>
@@ -2926,40 +3036,45 @@
       <c r="X23">
         <v>2.25</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z23">
         <v>2.268181818181818</v>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <v>24.95</v>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <v>40.18000030517578</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>90.63999938964844</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>50.45999908447266</v>
       </c>
-      <c r="AD23">
+      <c r="AE23">
         <v>75.40999908447266</v>
       </c>
-      <c r="AE23">
+      <c r="AF23">
         <v>7.540999908447266</v>
       </c>
-      <c r="AF23">
+      <c r="AG23">
         <v>6</v>
       </c>
-      <c r="AG23">
+      <c r="AH23">
         <v>543.8399963378906</v>
       </c>
-      <c r="AH23">
+      <c r="AI23">
         <v>37.70499954223633</v>
       </c>
-      <c r="AI23">
+      <c r="AJ23">
         <v>11.34090909090909</v>
       </c>
-      <c r="AJ23">
+      <c r="AK23">
         <v>49.04590863314542</v>
       </c>
     </row>
@@ -3037,40 +3152,45 @@
       <c r="X24">
         <v>0.88</v>
       </c>
-      <c r="Y24">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z24">
         <v>0.8558</v>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>8.558</v>
       </c>
-      <c r="AA24">
+      <c r="AB24">
         <v>14.10000038146973</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>28.48999977111816</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>14.38999938964844</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>22.94799938964844</v>
       </c>
-      <c r="AE24">
+      <c r="AF24">
         <v>2.294799938964844</v>
       </c>
-      <c r="AF24">
+      <c r="AG24">
         <v>18</v>
       </c>
-      <c r="AG24">
+      <c r="AH24">
         <v>512.819995880127</v>
       </c>
-      <c r="AH24">
+      <c r="AI24">
         <v>11.47399969482422</v>
       </c>
-      <c r="AI24">
+      <c r="AJ24">
         <v>4.279</v>
       </c>
-      <c r="AJ24">
+      <c r="AK24">
         <v>15.75299969482422</v>
       </c>
     </row>
@@ -3145,40 +3265,45 @@
       <c r="W25">
         <v>1.161</v>
       </c>
-      <c r="Y25">
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z25">
         <v>1.340444444444444</v>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <v>12.064</v>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <v>15.22999954223633</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>40.72999954223633</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>25.5</v>
       </c>
-      <c r="AD25">
+      <c r="AE25">
         <v>37.564</v>
       </c>
-      <c r="AE25">
+      <c r="AF25">
         <v>3.7564</v>
       </c>
-      <c r="AF25">
+      <c r="AG25">
         <v>13</v>
       </c>
-      <c r="AG25">
+      <c r="AH25">
         <v>529.4899940490723</v>
       </c>
-      <c r="AH25">
+      <c r="AI25">
         <v>18.782</v>
       </c>
-      <c r="AI25">
+      <c r="AJ25">
         <v>6.702222222222222</v>
       </c>
-      <c r="AJ25">
+      <c r="AK25">
         <v>25.48422222222222</v>
       </c>
     </row>
@@ -3259,40 +3384,45 @@
       <c r="X26">
         <v>0.4</v>
       </c>
-      <c r="Y26">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z26">
         <v>0.7636609090909091</v>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>8.400269999999999</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>20.81229782104492</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>47.61999893188477</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>26.80770111083984</v>
       </c>
-      <c r="AD26">
+      <c r="AE26">
         <v>35.20797111083984</v>
       </c>
-      <c r="AE26">
+      <c r="AF26">
         <v>3.520797111083984</v>
       </c>
-      <c r="AF26">
+      <c r="AG26">
         <v>11</v>
       </c>
-      <c r="AG26">
+      <c r="AH26">
         <v>523.8199882507324</v>
       </c>
-      <c r="AH26">
+      <c r="AI26">
         <v>17.60398555541992</v>
       </c>
-      <c r="AI26">
+      <c r="AJ26">
         <v>3.818304545454545</v>
       </c>
-      <c r="AJ26">
+      <c r="AK26">
         <v>21.42229010087447</v>
       </c>
     </row>
@@ -3373,40 +3503,45 @@
       <c r="X27">
         <v>0.205</v>
       </c>
-      <c r="Y27">
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z27">
         <v>0.6231818181818182</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>6.855</v>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <v>18.27000045776367</v>
       </c>
-      <c r="AB27">
+      <c r="AC27">
         <v>22.10000038146973</v>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <v>3.829999923706055</v>
       </c>
-      <c r="AD27">
+      <c r="AE27">
         <v>10.68499992370606</v>
       </c>
-      <c r="AE27">
+      <c r="AF27">
         <v>1.068499992370606</v>
       </c>
-      <c r="AF27">
+      <c r="AG27">
         <v>23</v>
       </c>
-      <c r="AG27">
+      <c r="AH27">
         <v>508.3000087738037</v>
       </c>
-      <c r="AH27">
+      <c r="AI27">
         <v>5.342499961853028</v>
       </c>
-      <c r="AI27">
+      <c r="AJ27">
         <v>3.115909090909091</v>
       </c>
-      <c r="AJ27">
+      <c r="AK27">
         <v>8.458409052762118</v>
       </c>
     </row>
@@ -3487,40 +3622,45 @@
       <c r="X28">
         <v>0.5</v>
       </c>
-      <c r="Y28">
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z28">
         <v>1.957272727272727</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>21.53</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>41.09000015258789</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>48.72000122070313</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>7.630001068115234</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>29.16000106811524</v>
       </c>
-      <c r="AE28">
+      <c r="AF28">
         <v>2.916000106811524</v>
       </c>
-      <c r="AF28">
+      <c r="AG28">
         <v>11</v>
       </c>
-      <c r="AG28">
+      <c r="AH28">
         <v>535.9200134277344</v>
       </c>
-      <c r="AH28">
+      <c r="AI28">
         <v>14.58000053405762</v>
       </c>
-      <c r="AI28">
+      <c r="AJ28">
         <v>9.786363636363637</v>
       </c>
-      <c r="AJ28">
+      <c r="AK28">
         <v>24.36636417042126</v>
       </c>
     </row>
@@ -3601,40 +3741,45 @@
       <c r="X29">
         <v>0.9</v>
       </c>
-      <c r="Y29">
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z29">
         <v>1.44</v>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>15.84</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>66.26999664306641</v>
       </c>
-      <c r="AB29">
+      <c r="AC29">
         <v>36.68999862670898</v>
       </c>
-      <c r="AC29">
+      <c r="AD29">
         <v>-29.57999801635742</v>
       </c>
-      <c r="AD29">
+      <c r="AE29">
         <v>-13.73999801635742</v>
       </c>
-      <c r="AE29">
+      <c r="AF29">
         <v>-1.373999801635742</v>
       </c>
-      <c r="AF29">
+      <c r="AG29">
         <v>14</v>
       </c>
-      <c r="AG29">
+      <c r="AH29">
         <v>513.6599807739258</v>
       </c>
-      <c r="AH29">
+      <c r="AI29">
         <v>-6.869999008178711</v>
       </c>
-      <c r="AI29">
+      <c r="AJ29">
         <v>7.199999999999999</v>
       </c>
-      <c r="AJ29">
+      <c r="AK29">
         <v>0.3300009918212883</v>
       </c>
     </row>
@@ -3715,40 +3860,45 @@
       <c r="X30">
         <v>1.34</v>
       </c>
-      <c r="Y30">
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z30">
         <v>2.883181818181818</v>
       </c>
-      <c r="Z30">
+      <c r="AA30">
         <v>31.715</v>
       </c>
-      <c r="AA30">
+      <c r="AB30">
         <v>36.77000045776367</v>
       </c>
-      <c r="AB30">
+      <c r="AC30">
         <v>54.04999923706055</v>
       </c>
-      <c r="AC30">
+      <c r="AD30">
         <v>17.27999877929688</v>
       </c>
-      <c r="AD30">
+      <c r="AE30">
         <v>48.99499877929688</v>
       </c>
-      <c r="AE30">
+      <c r="AF30">
         <v>4.899499877929688</v>
       </c>
-      <c r="AF30">
+      <c r="AG30">
         <v>10</v>
       </c>
-      <c r="AG30">
+      <c r="AH30">
         <v>540.4999923706055</v>
       </c>
-      <c r="AH30">
+      <c r="AI30">
         <v>24.49749938964844</v>
       </c>
-      <c r="AI30">
+      <c r="AJ30">
         <v>14.41590909090909</v>
       </c>
-      <c r="AJ30">
+      <c r="AK30">
         <v>38.91340848055753</v>
       </c>
     </row>
@@ -3829,40 +3979,45 @@
       <c r="X31">
         <v>0.65</v>
       </c>
-      <c r="Y31">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z31">
         <v>3.109363636363637</v>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <v>34.203</v>
       </c>
-      <c r="AA31">
+      <c r="AB31">
         <v>33.90000152587891</v>
       </c>
-      <c r="AB31">
+      <c r="AC31">
         <v>68.73999786376953</v>
       </c>
-      <c r="AC31">
+      <c r="AD31">
         <v>34.83999633789063</v>
       </c>
-      <c r="AD31">
+      <c r="AE31">
         <v>69.04299633789063</v>
       </c>
-      <c r="AE31">
+      <c r="AF31">
         <v>6.904299633789063</v>
       </c>
-      <c r="AF31">
+      <c r="AG31">
         <v>8</v>
       </c>
-      <c r="AG31">
+      <c r="AH31">
         <v>549.9199829101563</v>
       </c>
-      <c r="AH31">
+      <c r="AI31">
         <v>34.52149816894531</v>
       </c>
-      <c r="AI31">
+      <c r="AJ31">
         <v>15.54681818181818</v>
       </c>
-      <c r="AJ31">
+      <c r="AK31">
         <v>50.0683163507635</v>
       </c>
     </row>
@@ -3943,40 +4098,45 @@
       <c r="X32">
         <v>0.354</v>
       </c>
-      <c r="Y32">
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z32">
         <v>0.7749090909090909</v>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>8.523999999999999</v>
       </c>
-      <c r="AA32">
+      <c r="AB32">
         <v>17.81999969482422</v>
       </c>
-      <c r="AB32">
+      <c r="AC32">
         <v>38.22999954223633</v>
       </c>
-      <c r="AC32">
+      <c r="AD32">
         <v>20.40999984741211</v>
       </c>
-      <c r="AD32">
+      <c r="AE32">
         <v>28.93399984741211</v>
       </c>
-      <c r="AE32">
+      <c r="AF32">
         <v>2.893399984741211</v>
       </c>
-      <c r="AF32">
+      <c r="AG32">
         <v>14</v>
       </c>
-      <c r="AG32">
+      <c r="AH32">
         <v>535.2199935913086</v>
       </c>
-      <c r="AH32">
+      <c r="AI32">
         <v>14.46699992370606</v>
       </c>
-      <c r="AI32">
+      <c r="AJ32">
         <v>3.874545454545455</v>
       </c>
-      <c r="AJ32">
+      <c r="AK32">
         <v>18.34154537825151</v>
       </c>
     </row>
@@ -4057,40 +4217,45 @@
       <c r="X33">
         <v>0.7</v>
       </c>
-      <c r="Y33">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z33">
         <v>3.343636363636364</v>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <v>36.78</v>
       </c>
-      <c r="AA33">
+      <c r="AB33">
         <v>39.88000106811523</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>22.60000038146973</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>-17.28000068664551</v>
       </c>
-      <c r="AD33">
+      <c r="AE33">
         <v>19.49999931335449</v>
       </c>
-      <c r="AE33">
+      <c r="AF33">
         <v>1.949999931335449</v>
       </c>
-      <c r="AF33">
+      <c r="AG33">
         <v>23</v>
       </c>
-      <c r="AG33">
+      <c r="AH33">
         <v>519.8000087738037</v>
       </c>
-      <c r="AH33">
+      <c r="AI33">
         <v>9.749999656677247</v>
       </c>
-      <c r="AI33">
+      <c r="AJ33">
         <v>16.71818181818182</v>
       </c>
-      <c r="AJ33">
+      <c r="AK33">
         <v>26.46818147485907</v>
       </c>
     </row>
@@ -4165,40 +4330,45 @@
       <c r="X34">
         <v>0.621</v>
       </c>
-      <c r="Y34">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z34">
         <v>0.4551158888888889</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>4.096043</v>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <v>5.959052085876465</v>
       </c>
-      <c r="AB34">
+      <c r="AC34">
         <v>16.11000061035156</v>
       </c>
-      <c r="AC34">
+      <c r="AD34">
         <v>10.1509485244751</v>
       </c>
-      <c r="AD34">
+      <c r="AE34">
         <v>14.2469915244751</v>
       </c>
-      <c r="AE34">
+      <c r="AF34">
         <v>1.42469915244751</v>
       </c>
-      <c r="AF34">
+      <c r="AG34">
         <v>32</v>
       </c>
-      <c r="AG34">
+      <c r="AH34">
         <v>515.52001953125</v>
       </c>
-      <c r="AH34">
+      <c r="AI34">
         <v>7.123495762237548</v>
       </c>
-      <c r="AI34">
+      <c r="AJ34">
         <v>2.275579444444444</v>
       </c>
-      <c r="AJ34">
+      <c r="AK34">
         <v>9.399075206681992</v>
       </c>
     </row>
@@ -4270,40 +4440,45 @@
       <c r="X35">
         <v>1.05</v>
       </c>
-      <c r="Y35">
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z35">
         <v>4.45375</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>35.63</v>
       </c>
-      <c r="AA35">
+      <c r="AB35">
         <v>22.13999938964844</v>
       </c>
-      <c r="AB35">
+      <c r="AC35">
         <v>58.90999984741211</v>
       </c>
-      <c r="AC35">
+      <c r="AD35">
         <v>36.77000045776367</v>
       </c>
-      <c r="AD35">
+      <c r="AE35">
         <v>72.40000045776367</v>
       </c>
-      <c r="AE35">
+      <c r="AF35">
         <v>7.240000045776367</v>
       </c>
-      <c r="AF35">
+      <c r="AG35">
         <v>9</v>
       </c>
-      <c r="AG35">
+      <c r="AH35">
         <v>530.189998626709</v>
       </c>
-      <c r="AH35">
+      <c r="AI35">
         <v>36.20000022888183</v>
       </c>
-      <c r="AI35">
+      <c r="AJ35">
         <v>22.26875</v>
       </c>
-      <c r="AJ35">
+      <c r="AK35">
         <v>58.46875022888183</v>
       </c>
     </row>
@@ -4384,40 +4559,45 @@
       <c r="X36">
         <v>0.9299999999999999</v>
       </c>
-      <c r="Y36">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z36">
         <v>1.082818181818182</v>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <v>11.911</v>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <v>52.59000015258789</v>
       </c>
-      <c r="AB36">
+      <c r="AC36">
         <v>48.52000045776367</v>
       </c>
-      <c r="AC36">
+      <c r="AD36">
         <v>-4.069999694824219</v>
       </c>
-      <c r="AD36">
+      <c r="AE36">
         <v>7.841000305175781</v>
       </c>
-      <c r="AE36">
+      <c r="AF36">
         <v>0.784100030517578</v>
       </c>
-      <c r="AF36">
+      <c r="AG36">
         <v>11</v>
       </c>
-      <c r="AG36">
+      <c r="AH36">
         <v>533.7200050354004</v>
       </c>
-      <c r="AH36">
+      <c r="AI36">
         <v>3.92050015258789</v>
       </c>
-      <c r="AI36">
+      <c r="AJ36">
         <v>5.414090909090909</v>
       </c>
-      <c r="AJ36">
+      <c r="AK36">
         <v>9.3345910616788</v>
       </c>
     </row>
@@ -4498,40 +4678,45 @@
       <c r="X37">
         <v>1.4</v>
       </c>
-      <c r="Y37">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z37">
         <v>3.954545454545455</v>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>43.5</v>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <v>104.0599975585938</v>
       </c>
-      <c r="AB37">
+      <c r="AC37">
         <v>96.44999694824219</v>
       </c>
-      <c r="AC37">
+      <c r="AD37">
         <v>-7.610000610351563</v>
       </c>
-      <c r="AD37">
+      <c r="AE37">
         <v>35.88999938964844</v>
       </c>
-      <c r="AE37">
+      <c r="AF37">
         <v>3.588999938964844</v>
       </c>
-      <c r="AF37">
+      <c r="AG37">
         <v>6</v>
       </c>
-      <c r="AG37">
+      <c r="AH37">
         <v>578.6999816894531</v>
       </c>
-      <c r="AH37">
+      <c r="AI37">
         <v>17.94499969482422</v>
       </c>
-      <c r="AI37">
+      <c r="AJ37">
         <v>19.77272727272727</v>
       </c>
-      <c r="AJ37">
+      <c r="AK37">
         <v>37.71772696755149</v>
       </c>
     </row>
@@ -4612,40 +4797,45 @@
       <c r="X38">
         <v>0.265</v>
       </c>
-      <c r="Y38">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z38">
         <v>0.6113636363636363</v>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <v>6.725000000000001</v>
       </c>
-      <c r="AA38">
+      <c r="AB38">
         <v>14.35999965667725</v>
       </c>
-      <c r="AB38">
+      <c r="AC38">
         <v>28.35000038146973</v>
       </c>
-      <c r="AC38">
+      <c r="AD38">
         <v>13.99000072479248</v>
       </c>
-      <c r="AD38">
+      <c r="AE38">
         <v>20.71500072479248</v>
       </c>
-      <c r="AE38">
+      <c r="AF38">
         <v>2.071500072479248</v>
       </c>
-      <c r="AF38">
+      <c r="AG38">
         <v>18</v>
       </c>
-      <c r="AG38">
+      <c r="AH38">
         <v>510.3000068664551</v>
       </c>
-      <c r="AH38">
+      <c r="AI38">
         <v>10.35750036239624</v>
       </c>
-      <c r="AI38">
+      <c r="AJ38">
         <v>3.056818181818182</v>
       </c>
-      <c r="AJ38">
+      <c r="AK38">
         <v>13.41431854421442</v>
       </c>
     </row>
@@ -4726,40 +4916,45 @@
       <c r="X39">
         <v>0.672</v>
       </c>
-      <c r="Y39">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z39">
         <v>1.554090909090909</v>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>17.095</v>
       </c>
-      <c r="AA39">
+      <c r="AB39">
         <v>38.40999984741211</v>
       </c>
-      <c r="AB39">
+      <c r="AC39">
         <v>70.31999969482422</v>
       </c>
-      <c r="AC39">
+      <c r="AD39">
         <v>31.90999984741211</v>
       </c>
-      <c r="AD39">
+      <c r="AE39">
         <v>49.00499984741211</v>
       </c>
-      <c r="AE39">
+      <c r="AF39">
         <v>4.900499984741211</v>
       </c>
-      <c r="AF39">
+      <c r="AG39">
         <v>8</v>
       </c>
-      <c r="AG39">
+      <c r="AH39">
         <v>562.5599975585938</v>
       </c>
-      <c r="AH39">
+      <c r="AI39">
         <v>24.50249992370605</v>
       </c>
-      <c r="AI39">
+      <c r="AJ39">
         <v>7.770454545454545</v>
       </c>
-      <c r="AJ39">
+      <c r="AK39">
         <v>32.2729544691606</v>
       </c>
     </row>
@@ -4837,40 +5032,45 @@
       <c r="X40">
         <v>2</v>
       </c>
-      <c r="Y40">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z40">
         <v>1.5439</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>15.439</v>
       </c>
-      <c r="AA40">
+      <c r="AB40">
         <v>23.76000022888184</v>
       </c>
-      <c r="AB40">
+      <c r="AC40">
         <v>42.16999816894531</v>
       </c>
-      <c r="AC40">
+      <c r="AD40">
         <v>18.40999794006348</v>
       </c>
-      <c r="AD40">
+      <c r="AE40">
         <v>33.84899794006348</v>
       </c>
-      <c r="AE40">
+      <c r="AF40">
         <v>3.384899794006348</v>
       </c>
-      <c r="AF40">
+      <c r="AG40">
         <v>12</v>
       </c>
-      <c r="AG40">
+      <c r="AH40">
         <v>506.0399780273438</v>
       </c>
-      <c r="AH40">
+      <c r="AI40">
         <v>16.92449897003174</v>
       </c>
-      <c r="AI40">
+      <c r="AJ40">
         <v>7.7195</v>
       </c>
-      <c r="AJ40">
+      <c r="AK40">
         <v>24.64399897003174</v>
       </c>
     </row>
@@ -4951,40 +5151,45 @@
       <c r="X41">
         <v>0.48</v>
       </c>
-      <c r="Y41">
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z41">
         <v>1.745454545454545</v>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <v>19.2</v>
       </c>
-      <c r="AA41">
+      <c r="AB41">
         <v>21.95000076293945</v>
       </c>
-      <c r="AB41">
+      <c r="AC41">
         <v>18.23999977111816</v>
       </c>
-      <c r="AC41">
+      <c r="AD41">
         <v>-3.710000991821289</v>
       </c>
-      <c r="AD41">
+      <c r="AE41">
         <v>15.48999900817871</v>
       </c>
-      <c r="AE41">
+      <c r="AF41">
         <v>1.548999900817871</v>
       </c>
-      <c r="AF41">
+      <c r="AG41">
         <v>28</v>
       </c>
-      <c r="AG41">
+      <c r="AH41">
         <v>510.7199935913086</v>
       </c>
-      <c r="AH41">
+      <c r="AI41">
         <v>7.744999504089355</v>
       </c>
-      <c r="AI41">
+      <c r="AJ41">
         <v>8.727272727272727</v>
       </c>
-      <c r="AJ41">
+      <c r="AK41">
         <v>16.47227223136208</v>
       </c>
     </row>
@@ -5062,40 +5267,45 @@
       <c r="X42">
         <v>3.291</v>
       </c>
-      <c r="Y42">
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z42">
         <v>1.6139</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>16.139</v>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <v>24.14999961853027</v>
       </c>
-      <c r="AB42">
+      <c r="AC42">
         <v>35.5099983215332</v>
       </c>
-      <c r="AC42">
+      <c r="AD42">
         <v>11.35999870300293</v>
       </c>
-      <c r="AD42">
+      <c r="AE42">
         <v>27.49899870300293</v>
       </c>
-      <c r="AE42">
+      <c r="AF42">
         <v>2.749899870300293</v>
       </c>
-      <c r="AF42">
+      <c r="AG42">
         <v>15</v>
       </c>
-      <c r="AG42">
+      <c r="AH42">
         <v>532.649974822998</v>
       </c>
-      <c r="AH42">
+      <c r="AI42">
         <v>13.74949935150146</v>
       </c>
-      <c r="AI42">
+      <c r="AJ42">
         <v>8.069500000000001</v>
       </c>
-      <c r="AJ42">
+      <c r="AK42">
         <v>21.81899935150147</v>
       </c>
     </row>
@@ -5176,40 +5386,45 @@
       <c r="X43">
         <v>0.52</v>
       </c>
-      <c r="Y43">
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z43">
         <v>1.620909090909091</v>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <v>17.83</v>
       </c>
-      <c r="AA43">
+      <c r="AB43">
         <v>47.02000045776367</v>
       </c>
-      <c r="AB43">
+      <c r="AC43">
         <v>51.06999969482422</v>
       </c>
-      <c r="AC43">
+      <c r="AD43">
         <v>4.049999237060547</v>
       </c>
-      <c r="AD43">
+      <c r="AE43">
         <v>21.87999923706055</v>
       </c>
-      <c r="AE43">
+      <c r="AF43">
         <v>2.187999923706055</v>
       </c>
-      <c r="AF43">
+      <c r="AG43">
         <v>10</v>
       </c>
-      <c r="AG43">
+      <c r="AH43">
         <v>510.6999969482422</v>
       </c>
-      <c r="AH43">
+      <c r="AI43">
         <v>10.93999961853027</v>
       </c>
-      <c r="AI43">
+      <c r="AJ43">
         <v>8.104545454545454</v>
       </c>
-      <c r="AJ43">
+      <c r="AK43">
         <v>19.04454507307573</v>
       </c>
     </row>
@@ -5290,40 +5505,45 @@
       <c r="X44">
         <v>1.3</v>
       </c>
-      <c r="Y44">
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z44">
         <v>3.789090909090909</v>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <v>41.68</v>
       </c>
-      <c r="AA44">
+      <c r="AB44">
         <v>75.26000213623047</v>
       </c>
-      <c r="AB44">
+      <c r="AC44">
         <v>99.13999938964844</v>
       </c>
-      <c r="AC44">
+      <c r="AD44">
         <v>23.87999725341797</v>
       </c>
-      <c r="AD44">
+      <c r="AE44">
         <v>65.55999725341798</v>
       </c>
-      <c r="AE44">
+      <c r="AF44">
         <v>6.555999725341797</v>
       </c>
-      <c r="AF44">
+      <c r="AG44">
         <v>6</v>
       </c>
-      <c r="AG44">
+      <c r="AH44">
         <v>594.8399963378906</v>
       </c>
-      <c r="AH44">
+      <c r="AI44">
         <v>32.77999862670899</v>
       </c>
-      <c r="AI44">
+      <c r="AJ44">
         <v>18.94545454545455</v>
       </c>
-      <c r="AJ44">
+      <c r="AK44">
         <v>51.72545317216353</v>
       </c>
     </row>
@@ -5401,40 +5621,45 @@
       <c r="W45">
         <v>2.18</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z45">
         <v>1.8141</v>
       </c>
-      <c r="Z45">
+      <c r="AA45">
         <v>18.141</v>
       </c>
-      <c r="AA45">
+      <c r="AB45">
         <v>28.13999938964844</v>
       </c>
-      <c r="AB45">
+      <c r="AC45">
         <v>57.18000030517578</v>
       </c>
-      <c r="AC45">
+      <c r="AD45">
         <v>29.04000091552734</v>
       </c>
-      <c r="AD45">
+      <c r="AE45">
         <v>47.18100091552734</v>
       </c>
-      <c r="AE45">
+      <c r="AF45">
         <v>4.718100091552734</v>
       </c>
-      <c r="AF45">
+      <c r="AG45">
         <v>9</v>
       </c>
-      <c r="AG45">
+      <c r="AH45">
         <v>514.620002746582</v>
       </c>
-      <c r="AH45">
+      <c r="AI45">
         <v>23.59050045776367</v>
       </c>
-      <c r="AI45">
+      <c r="AJ45">
         <v>9.070499999999999</v>
       </c>
-      <c r="AJ45">
+      <c r="AK45">
         <v>32.66100045776367</v>
       </c>
     </row>
@@ -5515,40 +5740,45 @@
       <c r="X46">
         <v>0.52</v>
       </c>
-      <c r="Y46">
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z46">
         <v>1.516818181818182</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>16.685</v>
       </c>
-      <c r="AA46">
+      <c r="AB46">
         <v>51.36999893188477</v>
       </c>
-      <c r="AB46">
+      <c r="AC46">
         <v>56.84000015258789</v>
       </c>
-      <c r="AC46">
+      <c r="AD46">
         <v>5.470001220703125</v>
       </c>
-      <c r="AD46">
+      <c r="AE46">
         <v>22.15500122070312</v>
       </c>
-      <c r="AE46">
+      <c r="AF46">
         <v>2.215500122070313</v>
       </c>
-      <c r="AF46">
+      <c r="AG46">
         <v>9</v>
       </c>
-      <c r="AG46">
+      <c r="AH46">
         <v>511.560001373291</v>
       </c>
-      <c r="AH46">
+      <c r="AI46">
         <v>11.07750061035156</v>
       </c>
-      <c r="AI46">
+      <c r="AJ46">
         <v>7.584090909090909</v>
       </c>
-      <c r="AJ46">
+      <c r="AK46">
         <v>18.66159151944247</v>
       </c>
     </row>
@@ -5608,40 +5838,45 @@
       <c r="W47">
         <v>2.257</v>
       </c>
-      <c r="Y47">
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="Z47">
         <v>2.34775</v>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <v>9.391</v>
       </c>
-      <c r="AA47">
+      <c r="AB47">
         <v>32</v>
       </c>
-      <c r="AB47">
+      <c r="AC47">
         <v>71.59999847412109</v>
       </c>
-      <c r="AC47">
+      <c r="AD47">
         <v>39.59999847412109</v>
       </c>
-      <c r="AD47">
+      <c r="AE47">
         <v>48.99099847412109</v>
       </c>
-      <c r="AE47">
+      <c r="AF47">
         <v>4.899099847412109</v>
       </c>
-      <c r="AF47">
+      <c r="AG47">
         <v>7</v>
       </c>
-      <c r="AG47">
+      <c r="AH47">
         <v>501.1999893188477</v>
       </c>
-      <c r="AH47">
+      <c r="AI47">
         <v>24.49549923706055</v>
       </c>
-      <c r="AI47">
+      <c r="AJ47">
         <v>11.73875</v>
       </c>
-      <c r="AJ47">
+      <c r="AK47">
         <v>36.23424923706055</v>
       </c>
     </row>

--- a/ProductionBuild/fullviewfinancials.result.xlsx
+++ b/ProductionBuild/fullviewfinancials.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL21"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -673,79 +673,76 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NetEase Inc</t>
+          <t>Swisscom AG</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NTES</t>
+          <t>SCMWY</t>
         </is>
       </c>
       <c r="C3">
-        <v>43.06800079345703</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="D3">
-        <v>69.01399993896484</v>
+        <v>53.33000183105469</v>
       </c>
       <c r="E3">
-        <v>47.07400131225586</v>
+        <v>47.95000076293945</v>
       </c>
       <c r="F3">
-        <v>61.32799911499023</v>
+        <v>52.86000061035156</v>
       </c>
       <c r="G3">
-        <v>95.76999664306641</v>
+        <v>53.75</v>
       </c>
       <c r="H3">
-        <v>101.7799987792969</v>
+        <v>56.41999816894531</v>
       </c>
       <c r="I3">
-        <v>72.62999725341797</v>
+        <v>54.91999816894531</v>
       </c>
       <c r="J3">
-        <v>93.16000366210938</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="K3">
-        <v>89.20999908447266</v>
+        <v>56.02999877929688</v>
       </c>
       <c r="L3">
-        <v>137.6199951171875</v>
+        <v>72.79000091552734</v>
       </c>
       <c r="M3">
-        <v>113.2699966430664</v>
-      </c>
-      <c r="N3">
-        <v>0.458</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="O3">
-        <v>0.728</v>
+        <v>2.181</v>
       </c>
       <c r="P3">
-        <v>0.334</v>
+        <v>2.355</v>
       </c>
       <c r="Q3">
-        <v>1.96</v>
+        <v>2.183</v>
       </c>
       <c r="R3">
-        <v>0.9279999999999999</v>
+        <v>2.299</v>
       </c>
       <c r="S3">
-        <v>0.825</v>
+        <v>2.471</v>
       </c>
       <c r="T3">
-        <v>1.522</v>
+        <v>2.369</v>
       </c>
       <c r="U3">
-        <v>1.755</v>
+        <v>2.343</v>
       </c>
       <c r="V3">
-        <v>2.445</v>
+        <v>2.487</v>
       </c>
       <c r="W3">
-        <v>3.035</v>
+        <v>2.475</v>
       </c>
       <c r="X3">
-        <v>1.16</v>
+        <v>3.378</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -753,40 +750,40 @@
         </is>
       </c>
       <c r="Z3">
-        <v>1.377272727272727</v>
+        <v>2.4541</v>
       </c>
       <c r="AA3">
-        <v>15.15</v>
+        <v>24.541</v>
       </c>
       <c r="AB3">
-        <v>43.06800079345703</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="AC3">
-        <v>113.2699966430664</v>
+        <v>83.33000183105469</v>
       </c>
       <c r="AD3">
-        <v>70.20199584960938</v>
+        <v>38.59000015258789</v>
       </c>
       <c r="AE3">
-        <v>85.35199584960938</v>
+        <v>63.13100015258789</v>
       </c>
       <c r="AF3">
-        <v>8.535199584960939</v>
+        <v>6.313100015258788</v>
       </c>
       <c r="AG3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH3">
-        <v>566.349983215332</v>
+        <v>583.3100128173828</v>
       </c>
       <c r="AI3">
-        <v>42.67599792480469</v>
+        <v>31.56550007629394</v>
       </c>
       <c r="AJ3">
-        <v>6.886363636363636</v>
+        <v>12.2705</v>
       </c>
       <c r="AK3">
-        <v>49.56236156116832</v>
+        <v>43.83600007629394</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -797,76 +794,64 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Swisscom AG</t>
+          <t>SK Telecom Co Ltd</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SCMWY</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="C4">
-        <v>44.7400016784668</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="D4">
-        <v>53.33000183105469</v>
+        <v>45.98023223876953</v>
       </c>
       <c r="E4">
-        <v>47.95000076293945</v>
+        <v>44.15156555175781</v>
       </c>
       <c r="F4">
-        <v>52.86000061035156</v>
+        <v>38.07248687744141</v>
       </c>
       <c r="G4">
-        <v>53.75</v>
+        <v>40.32949066162109</v>
       </c>
       <c r="H4">
-        <v>56.41999816894531</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="I4">
-        <v>54.91999816894531</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="J4">
-        <v>60.18000030517578</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="K4">
-        <v>56.02999877929688</v>
+        <v>21.04000091552734</v>
       </c>
       <c r="L4">
-        <v>72.79000091552734</v>
+        <v>20.53000068664551</v>
       </c>
       <c r="M4">
-        <v>83.33000183105469</v>
-      </c>
-      <c r="O4">
-        <v>2.181</v>
-      </c>
-      <c r="P4">
-        <v>2.355</v>
-      </c>
-      <c r="Q4">
-        <v>2.183</v>
+        <v>38.81999969482422</v>
       </c>
       <c r="R4">
-        <v>2.299</v>
+        <v>0.15486</v>
       </c>
       <c r="S4">
-        <v>2.471</v>
+        <v>21.034244</v>
       </c>
       <c r="T4">
-        <v>2.369</v>
+        <v>1.402</v>
       </c>
       <c r="U4">
-        <v>2.343</v>
+        <v>1.468</v>
       </c>
       <c r="V4">
-        <v>2.487</v>
+        <v>1.002</v>
       </c>
       <c r="W4">
-        <v>2.475</v>
-      </c>
-      <c r="X4">
-        <v>3.378</v>
+        <v>0.738</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -874,40 +859,40 @@
         </is>
       </c>
       <c r="Z4">
-        <v>2.4541</v>
+        <v>4.299850666666666</v>
       </c>
       <c r="AA4">
-        <v>24.541</v>
+        <v>25.799104</v>
       </c>
       <c r="AB4">
-        <v>44.7400016784668</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="AC4">
-        <v>83.33000183105469</v>
+        <v>38.81999969482422</v>
       </c>
       <c r="AD4">
-        <v>38.59000015258789</v>
+        <v>4.388370513916016</v>
       </c>
       <c r="AE4">
-        <v>63.13100015258789</v>
+        <v>30.18747451391601</v>
       </c>
       <c r="AF4">
-        <v>6.313100015258788</v>
+        <v>3.018747451391601</v>
       </c>
       <c r="AG4">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AH4">
-        <v>583.3100128173828</v>
+        <v>504.6599960327148</v>
       </c>
       <c r="AI4">
-        <v>31.56550007629394</v>
+        <v>15.09373725695801</v>
       </c>
       <c r="AJ4">
-        <v>12.2705</v>
+        <v>21.49925333333333</v>
       </c>
       <c r="AK4">
-        <v>43.83600007629394</v>
+        <v>36.59299059029134</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -918,64 +903,76 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK Telecom Co Ltd</t>
+          <t>Elisa Corp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>ELMUY</t>
         </is>
       </c>
       <c r="C5">
-        <v>34.4316291809082</v>
+        <v>18.5</v>
       </c>
       <c r="D5">
-        <v>45.98023223876953</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="E5">
-        <v>44.15156555175781</v>
+        <v>21</v>
       </c>
       <c r="F5">
-        <v>38.07248687744141</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="G5">
-        <v>40.32949066162109</v>
+        <v>27.85000038146973</v>
       </c>
       <c r="H5">
-        <v>26.67000007629395</v>
+        <v>30.30999946594238</v>
       </c>
       <c r="I5">
-        <v>20.59000015258789</v>
+        <v>23.8700008392334</v>
       </c>
       <c r="J5">
-        <v>21.39999961853027</v>
+        <v>23.06999969482422</v>
       </c>
       <c r="K5">
-        <v>21.04000091552734</v>
+        <v>21.52000045776367</v>
       </c>
       <c r="L5">
-        <v>20.53000068664551</v>
+        <v>23.04500007629395</v>
       </c>
       <c r="M5">
-        <v>38.81999969482422</v>
+        <v>32.75</v>
+      </c>
+      <c r="O5">
+        <v>0.8031</v>
+      </c>
+      <c r="P5">
+        <v>1.005922</v>
+      </c>
+      <c r="Q5">
+        <v>0.987437</v>
       </c>
       <c r="R5">
-        <v>0.15486</v>
+        <v>1.006122</v>
       </c>
       <c r="S5">
-        <v>21.034244</v>
+        <v>1.17429</v>
       </c>
       <c r="T5">
-        <v>1.402</v>
+        <v>1.109562</v>
       </c>
       <c r="U5">
-        <v>1.468</v>
+        <v>1.17476</v>
       </c>
       <c r="V5">
-        <v>1.002</v>
+        <v>1.212532</v>
       </c>
       <c r="W5">
-        <v>0.738</v>
+        <v>1.345888</v>
+      </c>
+      <c r="X5">
+        <v>0.34533</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -983,40 +980,40 @@
         </is>
       </c>
       <c r="Z5">
-        <v>4.299850666666666</v>
+        <v>1.0164943</v>
       </c>
       <c r="AA5">
-        <v>25.799104</v>
+        <v>10.164943</v>
       </c>
       <c r="AB5">
-        <v>34.4316291809082</v>
+        <v>18.5</v>
       </c>
       <c r="AC5">
-        <v>38.81999969482422</v>
+        <v>32.75</v>
       </c>
       <c r="AD5">
-        <v>4.388370513916016</v>
+        <v>14.25</v>
       </c>
       <c r="AE5">
-        <v>30.18747451391601</v>
+        <v>24.414943</v>
       </c>
       <c r="AF5">
-        <v>3.018747451391601</v>
+        <v>2.4414943</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AH5">
-        <v>504.6599960327148</v>
+        <v>524</v>
       </c>
       <c r="AI5">
-        <v>15.09373725695801</v>
+        <v>12.2074715</v>
       </c>
       <c r="AJ5">
-        <v>21.49925333333333</v>
+        <v>5.0824715</v>
       </c>
       <c r="AK5">
-        <v>36.59299059029134</v>
+        <v>17.289943</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1027,79 +1024,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CAR Group Limited</t>
+          <t>Omnicom Group Inc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSXXY</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="C6">
-        <v>15.80000019073486</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="D6">
-        <v>22.94000053405762</v>
+        <v>72.83000183105469</v>
       </c>
       <c r="E6">
-        <v>15.3100004196167</v>
+        <v>73.23999786376953</v>
       </c>
       <c r="F6">
-        <v>23.37800025939941</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="G6">
-        <v>30.81999969482422</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="H6">
-        <v>37.70999908447266</v>
+        <v>73.26999664306641</v>
       </c>
       <c r="I6">
-        <v>27.90500068664551</v>
+        <v>81.56999969482422</v>
       </c>
       <c r="J6">
-        <v>42.40999984741211</v>
+        <v>86.51000213623047</v>
       </c>
       <c r="K6">
-        <v>45.5</v>
+        <v>86.04000091552734</v>
       </c>
       <c r="L6">
-        <v>40</v>
+        <v>80.75</v>
       </c>
       <c r="M6">
-        <v>36.77999877929688</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="N6">
-        <v>0.3</v>
+        <v>1.65</v>
       </c>
       <c r="O6">
-        <v>0.624</v>
+        <v>2.25</v>
       </c>
       <c r="P6">
-        <v>0.667</v>
+        <v>2.4</v>
       </c>
       <c r="Q6">
-        <v>0.631</v>
+        <v>2.6</v>
       </c>
       <c r="R6">
-        <v>0.6579999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="S6">
-        <v>0.855</v>
+        <v>2.8</v>
       </c>
       <c r="T6">
-        <v>0.708</v>
+        <v>2.8</v>
       </c>
       <c r="U6">
-        <v>0.989</v>
+        <v>2.8</v>
       </c>
       <c r="V6">
-        <v>0.958</v>
+        <v>2.8</v>
       </c>
       <c r="W6">
-        <v>0.483</v>
+        <v>2.9</v>
       </c>
       <c r="X6">
-        <v>0.603</v>
+        <v>0.8</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1107,40 +1104,40 @@
         </is>
       </c>
       <c r="Z6">
-        <v>0.6796363636363636</v>
+        <v>2.4</v>
       </c>
       <c r="AA6">
-        <v>7.476</v>
+        <v>26.4</v>
       </c>
       <c r="AB6">
-        <v>15.80000019073486</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="AC6">
-        <v>36.77999877929688</v>
+        <v>78.11000061035156</v>
       </c>
       <c r="AD6">
-        <v>20.97999858856201</v>
+        <v>-7</v>
       </c>
       <c r="AE6">
-        <v>28.45599858856201</v>
+        <v>19.4</v>
       </c>
       <c r="AF6">
-        <v>2.845599858856201</v>
+        <v>1.94</v>
       </c>
       <c r="AG6">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AH6">
-        <v>514.9199829101563</v>
+        <v>546.7700042724609</v>
       </c>
       <c r="AI6">
-        <v>14.22799929428101</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ6">
-        <v>3.398181818181818</v>
+        <v>12</v>
       </c>
       <c r="AK6">
-        <v>17.62618111246282</v>
+        <v>21.7</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1151,76 +1148,79 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chunghwa Telecom Co Ltd</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHT</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C7">
-        <v>31.54999923706055</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="D7">
-        <v>35.43999862670898</v>
+        <v>52.93000030517578</v>
       </c>
       <c r="E7">
-        <v>35.79000091552734</v>
+        <v>56.22000122070313</v>
       </c>
       <c r="F7">
-        <v>36.90000152587891</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="G7">
-        <v>38.61999893188477</v>
+        <v>58.75</v>
       </c>
       <c r="H7">
-        <v>42.20999908447266</v>
+        <v>51.95999908447266</v>
       </c>
       <c r="I7">
-        <v>36.59000015258789</v>
+        <v>39.40000152587891</v>
       </c>
       <c r="J7">
-        <v>39.06999969482422</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="K7">
-        <v>37.65000152587891</v>
+        <v>39.9900016784668</v>
       </c>
       <c r="L7">
-        <v>41.70999908447266</v>
+        <v>40.72999954223633</v>
       </c>
       <c r="M7">
-        <v>43.15000152587891</v>
+        <v>45.97999954223633</v>
       </c>
       <c r="N7">
-        <v>1.69</v>
+        <v>1.143</v>
       </c>
       <c r="O7">
-        <v>1.629</v>
+        <v>2.324</v>
       </c>
       <c r="P7">
-        <v>1.59</v>
+        <v>2.373</v>
       </c>
       <c r="Q7">
-        <v>1.443</v>
+        <v>2.424</v>
       </c>
       <c r="R7">
-        <v>1.419</v>
+        <v>2.473</v>
       </c>
       <c r="S7">
-        <v>1.551</v>
+        <v>2.524</v>
       </c>
       <c r="T7">
-        <v>1.591</v>
+        <v>2.573</v>
       </c>
       <c r="U7">
-        <v>1.529</v>
+        <v>2.624</v>
       </c>
       <c r="V7">
-        <v>1.462</v>
+        <v>2.673</v>
       </c>
       <c r="W7">
-        <v>1.669</v>
+        <v>2.724</v>
+      </c>
+      <c r="X7">
+        <v>1.398</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1228,40 +1228,40 @@
         </is>
       </c>
       <c r="Z7">
-        <v>1.5573</v>
+        <v>2.295727272727273</v>
       </c>
       <c r="AA7">
-        <v>15.573</v>
+        <v>25.253</v>
       </c>
       <c r="AB7">
-        <v>31.54999923706055</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="AC7">
-        <v>43.15000152587891</v>
+        <v>45.97999954223633</v>
       </c>
       <c r="AD7">
-        <v>11.60000228881836</v>
+        <v>-7.400001525878906</v>
       </c>
       <c r="AE7">
-        <v>27.17300228881836</v>
+        <v>17.85299847412109</v>
       </c>
       <c r="AF7">
-        <v>2.717300228881836</v>
+        <v>1.785299847412109</v>
       </c>
       <c r="AG7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7">
-        <v>517.8000183105469</v>
+        <v>505.7799949645996</v>
       </c>
       <c r="AI7">
-        <v>13.58650114440918</v>
+        <v>8.926499237060547</v>
       </c>
       <c r="AJ7">
-        <v>7.786499999999999</v>
+        <v>11.47863636363636</v>
       </c>
       <c r="AK7">
-        <v>21.37300114440918</v>
+        <v>20.40513560069691</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1272,76 +1272,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Elisa Corp</t>
+          <t>Orange SA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ELMUY</t>
+          <t>ORANY</t>
         </is>
       </c>
       <c r="C8">
-        <v>18.5</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="D8">
-        <v>21.14999961853027</v>
+        <v>17.39999961853027</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>16.19000053405762</v>
       </c>
       <c r="F8">
-        <v>26.79999923706055</v>
+        <v>14.59000015258789</v>
       </c>
       <c r="G8">
-        <v>27.85000038146973</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="H8">
-        <v>30.30999946594238</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I8">
-        <v>23.8700008392334</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="J8">
-        <v>23.06999969482422</v>
+        <v>11.43000030517578</v>
       </c>
       <c r="K8">
-        <v>21.52000045776367</v>
+        <v>9.840000152587891</v>
       </c>
       <c r="L8">
-        <v>23.04500007629395</v>
+        <v>16.69000053405762</v>
       </c>
       <c r="M8">
-        <v>32.75</v>
+        <v>20.45000076293945</v>
+      </c>
+      <c r="N8">
+        <v>0.676</v>
       </c>
       <c r="O8">
-        <v>0.8031</v>
+        <v>0.717</v>
       </c>
       <c r="P8">
-        <v>1.005922</v>
+        <v>0.8140000000000001</v>
       </c>
       <c r="Q8">
-        <v>0.987437</v>
+        <v>0.778</v>
       </c>
       <c r="R8">
-        <v>1.006122</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="S8">
-        <v>1.17429</v>
+        <v>0.944</v>
       </c>
       <c r="T8">
-        <v>1.109562</v>
+        <v>0.733</v>
       </c>
       <c r="U8">
-        <v>1.17476</v>
+        <v>0.759</v>
       </c>
       <c r="V8">
-        <v>1.212532</v>
+        <v>0.769</v>
       </c>
       <c r="W8">
-        <v>1.345888</v>
-      </c>
-      <c r="X8">
-        <v>0.34533</v>
+        <v>0.516</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1349,40 +1349,40 @@
         </is>
       </c>
       <c r="Z8">
-        <v>1.0164943</v>
+        <v>0.7399</v>
       </c>
       <c r="AA8">
-        <v>10.164943</v>
+        <v>7.399</v>
       </c>
       <c r="AB8">
-        <v>18.5</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="AC8">
-        <v>32.75</v>
+        <v>20.45000076293945</v>
       </c>
       <c r="AD8">
-        <v>14.25</v>
+        <v>5.310000419616699</v>
       </c>
       <c r="AE8">
-        <v>24.414943</v>
+        <v>12.7090004196167</v>
       </c>
       <c r="AF8">
-        <v>2.4414943</v>
+        <v>1.27090004196167</v>
       </c>
       <c r="AG8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AH8">
-        <v>524</v>
+        <v>511.2500190734863</v>
       </c>
       <c r="AI8">
-        <v>12.2074715</v>
+        <v>6.35450020980835</v>
       </c>
       <c r="AJ8">
-        <v>5.0824715</v>
+        <v>3.6995</v>
       </c>
       <c r="AK8">
-        <v>17.289943</v>
+        <v>10.05400020980835</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1393,79 +1393,76 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Deutsche Telekom AG</t>
+          <t>Telenor ASA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DTEGY</t>
+          <t>TELNY</t>
         </is>
       </c>
       <c r="C9">
-        <v>17.10000038146973</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="D9">
-        <v>17.65999984741211</v>
+        <v>21.38999938964844</v>
       </c>
       <c r="E9">
-        <v>16.97999954223633</v>
+        <v>19.3700008392334</v>
       </c>
       <c r="F9">
-        <v>16.29000091552734</v>
+        <v>17.90999984741211</v>
       </c>
       <c r="G9">
-        <v>18.27000045776367</v>
+        <v>17</v>
       </c>
       <c r="H9">
-        <v>18.51000022888184</v>
+        <v>15.68000030517578</v>
       </c>
       <c r="I9">
-        <v>19.97999954223633</v>
+        <v>9.289999961853027</v>
       </c>
       <c r="J9">
-        <v>24.1299991607666</v>
+        <v>11.48999977111816</v>
       </c>
       <c r="K9">
-        <v>29.85000038146973</v>
+        <v>11.14000034332275</v>
       </c>
       <c r="L9">
-        <v>32.70000076293945</v>
+        <v>14.60999965667725</v>
       </c>
       <c r="M9">
-        <v>32.34000015258789</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="N9">
-        <v>0.606</v>
+        <v>0.897</v>
       </c>
       <c r="O9">
-        <v>0.66</v>
+        <v>0.9470000000000001</v>
       </c>
       <c r="P9">
-        <v>0.798</v>
+        <v>1.547</v>
       </c>
       <c r="Q9">
-        <v>0.784</v>
+        <v>0.966</v>
       </c>
       <c r="R9">
-        <v>0.655</v>
+        <v>0.9430000000000001</v>
       </c>
       <c r="S9">
-        <v>0.715</v>
+        <v>1.064</v>
       </c>
       <c r="T9">
-        <v>0.7</v>
+        <v>1.018</v>
       </c>
       <c r="U9">
-        <v>0.745</v>
+        <v>0.887</v>
       </c>
       <c r="V9">
-        <v>0.835</v>
+        <v>0.897</v>
       </c>
       <c r="W9">
-        <v>1.023</v>
-      </c>
-      <c r="X9">
-        <v>1.159</v>
+        <v>0.9019999999999999</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1473,40 +1470,40 @@
         </is>
       </c>
       <c r="Z9">
-        <v>0.7890909090909091</v>
+        <v>1.0068</v>
       </c>
       <c r="AA9">
-        <v>8.68</v>
+        <v>10.068</v>
       </c>
       <c r="AB9">
-        <v>17.10000038146973</v>
+        <v>14.92000007629395</v>
       </c>
       <c r="AC9">
-        <v>32.34000015258789</v>
+        <v>17.45000076293945</v>
       </c>
       <c r="AD9">
-        <v>15.23999977111816</v>
+        <v>2.530000686645508</v>
       </c>
       <c r="AE9">
-        <v>23.91999977111816</v>
+        <v>12.59800068664551</v>
       </c>
       <c r="AF9">
-        <v>2.391999977111817</v>
+        <v>1.259800068664551</v>
       </c>
       <c r="AG9">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="AH9">
-        <v>517.4400024414063</v>
+        <v>506.0500221252441</v>
       </c>
       <c r="AI9">
-        <v>11.95999988555908</v>
+        <v>6.299000343322754</v>
       </c>
       <c r="AJ9">
-        <v>3.945454545454545</v>
+        <v>5.034000000000001</v>
       </c>
       <c r="AK9">
-        <v>15.90545443101363</v>
+        <v>11.33300034332276</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1517,76 +1514,76 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Singapore Telecommunications Ltd</t>
+          <t>Publicis Groupe SA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SGAPY</t>
+          <t>PUBGY</t>
         </is>
       </c>
       <c r="C10">
-        <v>24.94000053405762</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="D10">
-        <v>26.64999961853027</v>
+        <v>16.98999977111816</v>
       </c>
       <c r="E10">
-        <v>21.5</v>
+        <v>14.15999984741211</v>
       </c>
       <c r="F10">
-        <v>25.05999946594238</v>
+        <v>11.31999969482422</v>
       </c>
       <c r="G10">
-        <v>17.39999961853027</v>
+        <v>12.34000015258789</v>
       </c>
       <c r="H10">
-        <v>17.19000053405762</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="I10">
-        <v>19.10000038146973</v>
+        <v>15.86999988555908</v>
       </c>
       <c r="J10">
-        <v>18.69000053405762</v>
+        <v>23.18000030517578</v>
       </c>
       <c r="K10">
-        <v>22.53000068664551</v>
+        <v>26.53000068664551</v>
       </c>
       <c r="L10">
-        <v>35.40999984741211</v>
+        <v>25.8799991607666</v>
       </c>
       <c r="M10">
-        <v>37.47999954223633</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="N10">
-        <v>1.274</v>
+        <v>0.45</v>
       </c>
       <c r="O10">
-        <v>1.28</v>
+        <v>0.507</v>
       </c>
       <c r="P10">
-        <v>1.293</v>
+        <v>0.588</v>
       </c>
       <c r="Q10">
-        <v>1.278</v>
+        <v>0.593</v>
       </c>
       <c r="R10">
-        <v>0.763</v>
+        <v>0.343</v>
       </c>
       <c r="S10">
-        <v>0.512</v>
+        <v>0.604</v>
       </c>
       <c r="T10">
-        <v>0.861</v>
+        <v>0.642</v>
       </c>
       <c r="U10">
-        <v>0.959</v>
+        <v>0.776</v>
       </c>
       <c r="V10">
-        <v>1.249</v>
+        <v>0.923</v>
       </c>
       <c r="W10">
-        <v>0.773</v>
+        <v>1.059</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1594,40 +1591,40 @@
         </is>
       </c>
       <c r="Z10">
-        <v>1.0242</v>
+        <v>0.6485</v>
       </c>
       <c r="AA10">
-        <v>10.242</v>
+        <v>6.485</v>
       </c>
       <c r="AB10">
-        <v>24.94000053405762</v>
+        <v>17.20000076293945</v>
       </c>
       <c r="AC10">
-        <v>37.47999954223633</v>
+        <v>22.86000061035156</v>
       </c>
       <c r="AD10">
-        <v>12.53999900817871</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="AE10">
-        <v>22.78199900817871</v>
+        <v>12.14499984741211</v>
       </c>
       <c r="AF10">
-        <v>2.278199900817871</v>
+        <v>1.214499984741211</v>
       </c>
       <c r="AG10">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AH10">
-        <v>524.7199935913086</v>
+        <v>502.9200134277344</v>
       </c>
       <c r="AI10">
-        <v>11.39099950408936</v>
+        <v>6.072499923706054</v>
       </c>
       <c r="AJ10">
-        <v>5.121</v>
+        <v>3.2425</v>
       </c>
       <c r="AK10">
-        <v>16.51199950408936</v>
+        <v>9.314999923706054</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -1638,55 +1635,79 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Match Group Inc</t>
+          <t>PLDT Inc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MTCH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11">
-        <v>17.10000038146973</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="D11">
-        <v>31.30999946594238</v>
+        <v>30.07999992370605</v>
       </c>
       <c r="E11">
-        <v>42.77000045776367</v>
+        <v>21.3799991607666</v>
       </c>
       <c r="F11">
-        <v>82.11000061035156</v>
+        <v>19.98999977111816</v>
       </c>
       <c r="G11">
-        <v>151.1900024414063</v>
+        <v>27.90999984741211</v>
       </c>
       <c r="H11">
-        <v>132.25</v>
+        <v>35.72000122070313</v>
       </c>
       <c r="I11">
-        <v>41.4900016784668</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="J11">
-        <v>36.5</v>
+        <v>23.43000030517578</v>
       </c>
       <c r="K11">
-        <v>32.70999908447266</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="L11">
-        <v>32.29000091552734</v>
+        <v>21.73999977111816</v>
       </c>
       <c r="M11">
-        <v>36.52999877929688</v>
+        <v>20.94000053405762</v>
+      </c>
+      <c r="N11">
+        <v>1.042</v>
+      </c>
+      <c r="O11">
+        <v>1.497</v>
       </c>
       <c r="P11">
-        <v>2</v>
+        <v>0.534</v>
+      </c>
+      <c r="Q11">
+        <v>1.37</v>
+      </c>
+      <c r="R11">
+        <v>1.544</v>
+      </c>
+      <c r="S11">
+        <v>1.669</v>
+      </c>
+      <c r="T11">
+        <v>2.161</v>
+      </c>
+      <c r="U11">
+        <v>1.961</v>
+      </c>
+      <c r="V11">
+        <v>1.703</v>
       </c>
       <c r="W11">
-        <v>0.76</v>
+        <v>0.821</v>
       </c>
       <c r="X11">
-        <v>0.39</v>
+        <v>0.798</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1694,40 +1715,40 @@
         </is>
       </c>
       <c r="Z11">
-        <v>1.05</v>
+        <v>1.372727272727273</v>
       </c>
       <c r="AA11">
-        <v>3.15</v>
+        <v>15.1</v>
       </c>
       <c r="AB11">
-        <v>17.10000038146973</v>
+        <v>27.54999923706055</v>
       </c>
       <c r="AC11">
-        <v>36.52999877929688</v>
+        <v>20.94000053405762</v>
       </c>
       <c r="AD11">
-        <v>19.42999839782715</v>
+        <v>-6.60999870300293</v>
       </c>
       <c r="AE11">
-        <v>22.57999839782715</v>
+        <v>8.49000129699707</v>
       </c>
       <c r="AF11">
-        <v>2.257999839782715</v>
+        <v>0.849000129699707</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AH11">
-        <v>511.4199829101563</v>
+        <v>502.5600128173828</v>
       </c>
       <c r="AI11">
-        <v>11.28999919891357</v>
+        <v>4.245000648498535</v>
       </c>
       <c r="AJ11">
-        <v>5.25</v>
+        <v>6.863636363636364</v>
       </c>
       <c r="AK11">
-        <v>16.53999919891357</v>
+        <v>11.1086370121349</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -1738,79 +1759,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Omnicom Group Inc</t>
+          <t>Comcast Corp</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="C12">
-        <v>85.11000061035156</v>
+        <v>32.35707473754883</v>
       </c>
       <c r="D12">
-        <v>72.83000183105469</v>
+        <v>37.5351448059082</v>
       </c>
       <c r="E12">
-        <v>73.23999786376953</v>
+        <v>31.91190338134766</v>
       </c>
       <c r="F12">
-        <v>81.01999664306641</v>
+        <v>42.14620590209961</v>
       </c>
       <c r="G12">
-        <v>62.36999893188477</v>
+        <v>49.10965347290039</v>
       </c>
       <c r="H12">
-        <v>73.26999664306641</v>
+        <v>47.16963577270508</v>
       </c>
       <c r="I12">
-        <v>81.56999969482422</v>
+        <v>32.77413177490234</v>
       </c>
       <c r="J12">
-        <v>86.51000213623047</v>
+        <v>41.09653091430664</v>
       </c>
       <c r="K12">
-        <v>86.04000091552734</v>
+        <v>35.17338180541992</v>
       </c>
       <c r="L12">
-        <v>80.75</v>
+        <v>28.01312065124512</v>
       </c>
       <c r="M12">
-        <v>78.11000061035156</v>
+        <v>29.3700008392334</v>
       </c>
       <c r="N12">
-        <v>1.65</v>
+        <v>0.386598</v>
       </c>
       <c r="O12">
-        <v>2.25</v>
+        <v>0.444237</v>
       </c>
       <c r="P12">
-        <v>2.4</v>
+        <v>0.860355</v>
       </c>
       <c r="Q12">
-        <v>2.6</v>
+        <v>0.5904389999999999</v>
       </c>
       <c r="R12">
-        <v>2.6</v>
+        <v>0.843487</v>
       </c>
       <c r="S12">
-        <v>2.8</v>
+        <v>0.9184640000000001</v>
       </c>
       <c r="T12">
-        <v>2.8</v>
+        <v>0.99344</v>
       </c>
       <c r="U12">
-        <v>2.8</v>
+        <v>1.068416</v>
       </c>
       <c r="V12">
-        <v>2.8</v>
+        <v>1.143392</v>
       </c>
       <c r="W12">
-        <v>2.9</v>
+        <v>1.218368</v>
       </c>
       <c r="X12">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1818,40 +1839,40 @@
         </is>
       </c>
       <c r="Z12">
-        <v>2.4</v>
+        <v>0.8297450909090909</v>
       </c>
       <c r="AA12">
-        <v>26.4</v>
+        <v>9.127196</v>
       </c>
       <c r="AB12">
-        <v>85.11000061035156</v>
+        <v>32.35707473754883</v>
       </c>
       <c r="AC12">
-        <v>78.11000061035156</v>
+        <v>29.3700008392334</v>
       </c>
       <c r="AD12">
-        <v>-7</v>
+        <v>-2.98707389831543</v>
       </c>
       <c r="AE12">
-        <v>19.4</v>
+        <v>6.14012210168457</v>
       </c>
       <c r="AF12">
-        <v>1.94</v>
+        <v>0.614012210168457</v>
       </c>
       <c r="AG12">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AH12">
-        <v>546.7700042724609</v>
+        <v>528.6600151062012</v>
       </c>
       <c r="AI12">
-        <v>9.699999999999999</v>
+        <v>3.070061050842285</v>
       </c>
       <c r="AJ12">
-        <v>12</v>
+        <v>4.148725454545454</v>
       </c>
       <c r="AK12">
-        <v>21.7</v>
+        <v>7.218786505387739</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -1862,79 +1883,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>BCE Inc.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>BCE</t>
         </is>
       </c>
       <c r="C13">
-        <v>53.38000106811523</v>
+        <v>43.2400016784668</v>
       </c>
       <c r="D13">
-        <v>52.93000030517578</v>
+        <v>48.0099983215332</v>
       </c>
       <c r="E13">
-        <v>56.22000122070313</v>
+        <v>39.52999877929688</v>
       </c>
       <c r="F13">
-        <v>61.40000152587891</v>
+        <v>46.34999847412109</v>
       </c>
       <c r="G13">
-        <v>58.75</v>
+        <v>42.79999923706055</v>
       </c>
       <c r="H13">
-        <v>51.95999908447266</v>
+        <v>52.04000091552734</v>
       </c>
       <c r="I13">
-        <v>39.40000152587891</v>
+        <v>43.95000076293945</v>
       </c>
       <c r="J13">
-        <v>37.70000076293945</v>
+        <v>39.38000106811523</v>
       </c>
       <c r="K13">
-        <v>39.9900016784668</v>
+        <v>23.18000030517578</v>
       </c>
       <c r="L13">
-        <v>40.72999954223633</v>
+        <v>23.81999969482422</v>
       </c>
       <c r="M13">
-        <v>45.97999954223633</v>
+        <v>23.72999954223633</v>
       </c>
       <c r="N13">
-        <v>1.143</v>
+        <v>1.577</v>
       </c>
       <c r="O13">
-        <v>2.324</v>
+        <v>2.221</v>
       </c>
       <c r="P13">
-        <v>2.373</v>
+        <v>1.744</v>
       </c>
       <c r="Q13">
-        <v>2.424</v>
+        <v>2.391</v>
       </c>
       <c r="R13">
-        <v>2.473</v>
+        <v>2.493</v>
       </c>
       <c r="S13">
-        <v>2.524</v>
+        <v>2.793</v>
       </c>
       <c r="T13">
-        <v>2.573</v>
+        <v>2.814</v>
       </c>
       <c r="U13">
-        <v>2.624</v>
+        <v>2.862</v>
       </c>
       <c r="V13">
-        <v>2.673</v>
+        <v>2.896</v>
       </c>
       <c r="W13">
-        <v>2.724</v>
+        <v>1.663</v>
       </c>
       <c r="X13">
-        <v>1.398</v>
+        <v>0.319</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1942,40 +1963,40 @@
         </is>
       </c>
       <c r="Z13">
-        <v>2.295727272727273</v>
+        <v>2.161181818181818</v>
       </c>
       <c r="AA13">
-        <v>25.253</v>
+        <v>23.773</v>
       </c>
       <c r="AB13">
-        <v>53.38000106811523</v>
+        <v>43.2400016784668</v>
       </c>
       <c r="AC13">
-        <v>45.97999954223633</v>
+        <v>23.72999954223633</v>
       </c>
       <c r="AD13">
-        <v>-7.400001525878906</v>
+        <v>-19.51000213623047</v>
       </c>
       <c r="AE13">
-        <v>17.85299847412109</v>
+        <v>4.262997863769531</v>
       </c>
       <c r="AF13">
-        <v>1.785299847412109</v>
+        <v>0.4262997863769531</v>
       </c>
       <c r="AG13">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AH13">
-        <v>505.7799949645996</v>
+        <v>522.0599899291992</v>
       </c>
       <c r="AI13">
-        <v>8.926499237060547</v>
+        <v>2.131498931884765</v>
       </c>
       <c r="AJ13">
-        <v>11.47863636363636</v>
+        <v>10.80590909090909</v>
       </c>
       <c r="AK13">
-        <v>20.40513560069691</v>
+        <v>12.93740802279386</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -1986,76 +2007,76 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>America Movil SAB de CV</t>
+          <t>Perusahaan Perseroan (Persero) PT Telekomunikasi I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AMX</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="C14">
-        <v>12.56999969482422</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="D14">
-        <v>17.14999961853027</v>
+        <v>32.22000122070313</v>
       </c>
       <c r="E14">
-        <v>14.25</v>
+        <v>26.20999908447266</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>28.5</v>
       </c>
       <c r="G14">
-        <v>14.53999996185303</v>
+        <v>23.52000045776367</v>
       </c>
       <c r="H14">
-        <v>21.11000061035156</v>
+        <v>28.98999977111816</v>
       </c>
       <c r="I14">
-        <v>18.20000076293945</v>
+        <v>23.85000038146973</v>
       </c>
       <c r="J14">
-        <v>18.52000045776367</v>
+        <v>25.76000022888184</v>
       </c>
       <c r="K14">
-        <v>14.3100004196167</v>
+        <v>16.45000076293945</v>
       </c>
       <c r="L14">
-        <v>20.67000007629395</v>
+        <v>21.04999923706055</v>
       </c>
       <c r="M14">
-        <v>25.72999954223633</v>
+        <v>17.68000030517578</v>
       </c>
       <c r="N14">
-        <v>0.302</v>
+        <v>0.8615</v>
       </c>
       <c r="O14">
-        <v>0.327</v>
+        <v>0.881</v>
       </c>
       <c r="P14">
-        <v>0.319</v>
+        <v>1.203</v>
       </c>
       <c r="Q14">
-        <v>0.366</v>
+        <v>1.137</v>
       </c>
       <c r="R14">
-        <v>0.352</v>
+        <v>1.08</v>
       </c>
       <c r="S14">
-        <v>0.397</v>
+        <v>1.177</v>
       </c>
       <c r="T14">
-        <v>0.802</v>
+        <v>1.039</v>
       </c>
       <c r="U14">
-        <v>0.525</v>
+        <v>1.13</v>
       </c>
       <c r="V14">
-        <v>0.506</v>
+        <v>1.112</v>
       </c>
       <c r="W14">
-        <v>0.277</v>
+        <v>1.287</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -2063,40 +2084,40 @@
         </is>
       </c>
       <c r="Z14">
-        <v>0.4173</v>
+        <v>1.09075</v>
       </c>
       <c r="AA14">
-        <v>4.173</v>
+        <v>10.9075</v>
       </c>
       <c r="AB14">
-        <v>12.56999969482422</v>
+        <v>29.15999984741211</v>
       </c>
       <c r="AC14">
-        <v>25.72999954223633</v>
+        <v>17.68000030517578</v>
       </c>
       <c r="AD14">
-        <v>13.15999984741211</v>
+        <v>-11.47999954223633</v>
       </c>
       <c r="AE14">
-        <v>17.33299984741211</v>
+        <v>-0.5724995422363275</v>
       </c>
       <c r="AF14">
-        <v>1.733299984741211</v>
+        <v>-0.05724995422363275</v>
       </c>
       <c r="AG14">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AH14">
-        <v>514.5999908447266</v>
+        <v>512.7200088500977</v>
       </c>
       <c r="AI14">
-        <v>8.666499923706056</v>
+        <v>-0.2862497711181637</v>
       </c>
       <c r="AJ14">
-        <v>2.0865</v>
+        <v>5.45375</v>
       </c>
       <c r="AK14">
-        <v>10.75299992370606</v>
+        <v>5.167500228881837</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2107,79 +2128,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rogers Communications Inc</t>
+          <t>Sirius XM Holdings Inc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RCI</t>
+          <t>SIRI</t>
         </is>
       </c>
       <c r="C15">
-        <v>38.58000183105469</v>
+        <v>44.5</v>
       </c>
       <c r="D15">
-        <v>50.93000030517578</v>
+        <v>53.59999847412109</v>
       </c>
       <c r="E15">
-        <v>51.2599983215332</v>
+        <v>57.09999847412109</v>
       </c>
       <c r="F15">
-        <v>49.66999816894531</v>
+        <v>71.5</v>
       </c>
       <c r="G15">
-        <v>46.59000015258789</v>
+        <v>63.70000076293945</v>
       </c>
       <c r="H15">
-        <v>47.63000106811523</v>
+        <v>63.5</v>
       </c>
       <c r="I15">
-        <v>46.84000015258789</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="J15">
-        <v>46.81000137329102</v>
+        <v>54.70000076293945</v>
       </c>
       <c r="K15">
-        <v>30.72999954223633</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="L15">
-        <v>37.72999954223633</v>
+        <v>20</v>
       </c>
       <c r="M15">
-        <v>37.47999954223633</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="N15">
-        <v>1.114</v>
+        <v>0.1</v>
       </c>
       <c r="O15">
-        <v>1.478</v>
+        <v>0.41</v>
       </c>
       <c r="P15">
-        <v>1.471</v>
+        <v>0.45</v>
       </c>
       <c r="Q15">
-        <v>1.503</v>
+        <v>0.49</v>
       </c>
       <c r="R15">
-        <v>1.519</v>
+        <v>0.54</v>
       </c>
       <c r="S15">
-        <v>1.598</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="T15">
-        <v>1.533</v>
+        <v>3.4</v>
       </c>
       <c r="U15">
-        <v>1.471</v>
+        <v>0.99</v>
       </c>
       <c r="V15">
-        <v>1.456</v>
+        <v>1.08</v>
       </c>
       <c r="W15">
-        <v>1.075</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
-        <v>0.368</v>
+        <v>0.27</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -2187,40 +2208,40 @@
         </is>
       </c>
       <c r="Z15">
-        <v>1.326</v>
+        <v>0.8618181818181818</v>
       </c>
       <c r="AA15">
-        <v>14.586</v>
+        <v>9.48</v>
       </c>
       <c r="AB15">
-        <v>38.58000183105469</v>
+        <v>44.5</v>
       </c>
       <c r="AC15">
-        <v>37.47999954223633</v>
+        <v>28.05999946594238</v>
       </c>
       <c r="AD15">
-        <v>-1.100002288818359</v>
+        <v>-16.44000053405762</v>
       </c>
       <c r="AE15">
-        <v>13.48599771118164</v>
+        <v>-6.960000534057617</v>
       </c>
       <c r="AF15">
-        <v>1.348599771118164</v>
+        <v>-0.6960000534057617</v>
       </c>
       <c r="AG15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AH15">
-        <v>524.7199935913086</v>
+        <v>505.0799903869629</v>
       </c>
       <c r="AI15">
-        <v>6.74299885559082</v>
+        <v>-3.480000267028808</v>
       </c>
       <c r="AJ15">
-        <v>6.630000000000001</v>
+        <v>4.309090909090909</v>
       </c>
       <c r="AK15">
-        <v>13.37299885559082</v>
+        <v>0.8290906420621003</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -2231,76 +2252,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Orange SA</t>
+          <t>Millicom International Cellular SA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORANY</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>15.14000034332275</v>
-      </c>
-      <c r="D16">
-        <v>17.39999961853027</v>
-      </c>
-      <c r="E16">
-        <v>16.19000053405762</v>
+          <t>TIGO</t>
+        </is>
       </c>
       <c r="F16">
-        <v>14.59000015258789</v>
+        <v>48.22999954223633</v>
       </c>
       <c r="G16">
-        <v>11.85999965667725</v>
+        <v>38.77999877929688</v>
       </c>
       <c r="H16">
-        <v>10.55000019073486</v>
+        <v>28.45000076293945</v>
       </c>
       <c r="I16">
-        <v>9.880000114440918</v>
+        <v>12.63000011444092</v>
       </c>
       <c r="J16">
-        <v>11.43000030517578</v>
+        <v>18</v>
       </c>
       <c r="K16">
-        <v>9.840000152587891</v>
+        <v>25.01000022888184</v>
       </c>
       <c r="L16">
-        <v>16.69000053405762</v>
+        <v>55.43999862670898</v>
       </c>
       <c r="M16">
-        <v>20.45000076293945</v>
-      </c>
-      <c r="N16">
-        <v>0.676</v>
-      </c>
-      <c r="O16">
-        <v>0.717</v>
-      </c>
-      <c r="P16">
-        <v>0.8140000000000001</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="Q16">
-        <v>0.778</v>
-      </c>
-      <c r="R16">
-        <v>0.6929999999999999</v>
-      </c>
-      <c r="S16">
-        <v>0.944</v>
-      </c>
-      <c r="T16">
-        <v>0.733</v>
-      </c>
-      <c r="U16">
-        <v>0.759</v>
-      </c>
-      <c r="V16">
-        <v>0.769</v>
+        <v>2.64</v>
       </c>
       <c r="W16">
-        <v>0.516</v>
+        <v>4.5</v>
+      </c>
+      <c r="X16">
+        <v>2.75</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -2308,626 +2299,24 @@
         </is>
       </c>
       <c r="Z16">
-        <v>0.7399</v>
+        <v>3.296666666666667</v>
       </c>
       <c r="AA16">
-        <v>7.399</v>
-      </c>
-      <c r="AB16">
-        <v>15.14000034332275</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AC16">
-        <v>20.45000076293945</v>
-      </c>
-      <c r="AD16">
-        <v>5.310000419616699</v>
-      </c>
-      <c r="AE16">
-        <v>12.7090004196167</v>
-      </c>
-      <c r="AF16">
-        <v>1.27090004196167</v>
+        <v>83.15000152587891</v>
       </c>
       <c r="AG16">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="AH16">
-        <v>511.2500190734863</v>
-      </c>
-      <c r="AI16">
-        <v>6.35450020980835</v>
+        <v>582.0500106811523</v>
       </c>
       <c r="AJ16">
-        <v>3.6995</v>
-      </c>
-      <c r="AK16">
-        <v>10.05400020980835</v>
+        <v>16.48333333333333</v>
       </c>
       <c r="AL16" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Telenor ASA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>TELNY</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>14.92000007629395</v>
-      </c>
-      <c r="D17">
-        <v>21.38999938964844</v>
-      </c>
-      <c r="E17">
-        <v>19.3700008392334</v>
-      </c>
-      <c r="F17">
-        <v>17.90999984741211</v>
-      </c>
-      <c r="G17">
-        <v>17</v>
-      </c>
-      <c r="H17">
-        <v>15.68000030517578</v>
-      </c>
-      <c r="I17">
-        <v>9.289999961853027</v>
-      </c>
-      <c r="J17">
-        <v>11.48999977111816</v>
-      </c>
-      <c r="K17">
-        <v>11.14000034332275</v>
-      </c>
-      <c r="L17">
-        <v>14.60999965667725</v>
-      </c>
-      <c r="M17">
-        <v>17.45000076293945</v>
-      </c>
-      <c r="N17">
-        <v>0.897</v>
-      </c>
-      <c r="O17">
-        <v>0.9470000000000001</v>
-      </c>
-      <c r="P17">
-        <v>1.547</v>
-      </c>
-      <c r="Q17">
-        <v>0.966</v>
-      </c>
-      <c r="R17">
-        <v>0.9430000000000001</v>
-      </c>
-      <c r="S17">
-        <v>1.064</v>
-      </c>
-      <c r="T17">
-        <v>1.018</v>
-      </c>
-      <c r="U17">
-        <v>0.887</v>
-      </c>
-      <c r="V17">
-        <v>0.897</v>
-      </c>
-      <c r="W17">
-        <v>0.9019999999999999</v>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Z17">
-        <v>1.0068</v>
-      </c>
-      <c r="AA17">
-        <v>10.068</v>
-      </c>
-      <c r="AB17">
-        <v>14.92000007629395</v>
-      </c>
-      <c r="AC17">
-        <v>17.45000076293945</v>
-      </c>
-      <c r="AD17">
-        <v>2.530000686645508</v>
-      </c>
-      <c r="AE17">
-        <v>12.59800068664551</v>
-      </c>
-      <c r="AF17">
-        <v>1.259800068664551</v>
-      </c>
-      <c r="AG17">
-        <v>29</v>
-      </c>
-      <c r="AH17">
-        <v>506.0500221252441</v>
-      </c>
-      <c r="AI17">
-        <v>6.299000343322754</v>
-      </c>
-      <c r="AJ17">
-        <v>5.034000000000001</v>
-      </c>
-      <c r="AK17">
-        <v>11.33300034332276</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Publicis Groupe SA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>PUBGY</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>17.20000076293945</v>
-      </c>
-      <c r="D18">
-        <v>16.98999977111816</v>
-      </c>
-      <c r="E18">
-        <v>14.15999984741211</v>
-      </c>
-      <c r="F18">
-        <v>11.31999969482422</v>
-      </c>
-      <c r="G18">
-        <v>12.34000015258789</v>
-      </c>
-      <c r="H18">
-        <v>16.89999961853027</v>
-      </c>
-      <c r="I18">
-        <v>15.86999988555908</v>
-      </c>
-      <c r="J18">
-        <v>23.18000030517578</v>
-      </c>
-      <c r="K18">
-        <v>26.53000068664551</v>
-      </c>
-      <c r="L18">
-        <v>25.8799991607666</v>
-      </c>
-      <c r="M18">
-        <v>22.86000061035156</v>
-      </c>
-      <c r="N18">
-        <v>0.45</v>
-      </c>
-      <c r="O18">
-        <v>0.507</v>
-      </c>
-      <c r="P18">
-        <v>0.588</v>
-      </c>
-      <c r="Q18">
-        <v>0.593</v>
-      </c>
-      <c r="R18">
-        <v>0.343</v>
-      </c>
-      <c r="S18">
-        <v>0.604</v>
-      </c>
-      <c r="T18">
-        <v>0.642</v>
-      </c>
-      <c r="U18">
-        <v>0.776</v>
-      </c>
-      <c r="V18">
-        <v>0.923</v>
-      </c>
-      <c r="W18">
-        <v>1.059</v>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Z18">
-        <v>0.6485</v>
-      </c>
-      <c r="AA18">
-        <v>6.485</v>
-      </c>
-      <c r="AB18">
-        <v>17.20000076293945</v>
-      </c>
-      <c r="AC18">
-        <v>22.86000061035156</v>
-      </c>
-      <c r="AD18">
-        <v>5.659999847412109</v>
-      </c>
-      <c r="AE18">
-        <v>12.14499984741211</v>
-      </c>
-      <c r="AF18">
-        <v>1.214499984741211</v>
-      </c>
-      <c r="AG18">
-        <v>22</v>
-      </c>
-      <c r="AH18">
-        <v>502.9200134277344</v>
-      </c>
-      <c r="AI18">
-        <v>6.072499923706054</v>
-      </c>
-      <c r="AJ18">
-        <v>3.2425</v>
-      </c>
-      <c r="AK18">
-        <v>9.314999923706054</v>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Informa Plc</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>IFJPY</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>16.79999923706055</v>
-      </c>
-      <c r="D19">
-        <v>19.65999984741211</v>
-      </c>
-      <c r="E19">
-        <v>16.1299991607666</v>
-      </c>
-      <c r="F19">
-        <v>23.07999992370605</v>
-      </c>
-      <c r="G19">
-        <v>14.97000026702881</v>
-      </c>
-      <c r="H19">
-        <v>14.15999984741211</v>
-      </c>
-      <c r="I19">
-        <v>15.01000022888184</v>
-      </c>
-      <c r="J19">
-        <v>20.05999946594238</v>
-      </c>
-      <c r="K19">
-        <v>20.14999961853027</v>
-      </c>
-      <c r="L19">
-        <v>24.09000015258789</v>
-      </c>
-      <c r="M19">
-        <v>22.36000061035156</v>
-      </c>
-      <c r="N19">
-        <v>1.845</v>
-      </c>
-      <c r="O19">
-        <v>0.494</v>
-      </c>
-      <c r="P19">
-        <v>0.5720000000000001</v>
-      </c>
-      <c r="Q19">
-        <v>0.579</v>
-      </c>
-      <c r="T19">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="U19">
-        <v>0.32</v>
-      </c>
-      <c r="V19">
-        <v>0.473</v>
-      </c>
-      <c r="W19">
-        <v>0.5389999999999999</v>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Z19">
-        <v>0.61175</v>
-      </c>
-      <c r="AA19">
-        <v>4.894</v>
-      </c>
-      <c r="AB19">
-        <v>16.79999923706055</v>
-      </c>
-      <c r="AC19">
-        <v>22.36000061035156</v>
-      </c>
-      <c r="AD19">
-        <v>5.560001373291016</v>
-      </c>
-      <c r="AE19">
-        <v>10.45400137329102</v>
-      </c>
-      <c r="AF19">
-        <v>1.045400137329102</v>
-      </c>
-      <c r="AG19">
-        <v>23</v>
-      </c>
-      <c r="AH19">
-        <v>514.2800140380859</v>
-      </c>
-      <c r="AI19">
-        <v>5.227000686645508</v>
-      </c>
-      <c r="AJ19">
-        <v>3.05875</v>
-      </c>
-      <c r="AK19">
-        <v>8.285750686645507</v>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>KT Corporation</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>KT</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>14.09000015258789</v>
-      </c>
-      <c r="D20">
-        <v>15.60999965667725</v>
-      </c>
-      <c r="E20">
-        <v>14.22000026702881</v>
-      </c>
-      <c r="F20">
-        <v>11.60000038146973</v>
-      </c>
-      <c r="G20">
-        <v>11.01000022888184</v>
-      </c>
-      <c r="H20">
-        <v>12.56999969482422</v>
-      </c>
-      <c r="I20">
-        <v>13.5</v>
-      </c>
-      <c r="J20">
-        <v>13.4399995803833</v>
-      </c>
-      <c r="K20">
-        <v>15.52000045776367</v>
-      </c>
-      <c r="L20">
-        <v>18.96999931335449</v>
-      </c>
-      <c r="M20">
-        <v>21.84000015258789</v>
-      </c>
-      <c r="T20">
-        <v>0.729</v>
-      </c>
-      <c r="U20">
-        <v>0.711</v>
-      </c>
-      <c r="V20">
-        <v>0.5429999999999999</v>
-      </c>
-      <c r="W20">
-        <v>0.6</v>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Z20">
-        <v>0.6457499999999999</v>
-      </c>
-      <c r="AA20">
-        <v>2.583</v>
-      </c>
-      <c r="AB20">
-        <v>14.09000015258789</v>
-      </c>
-      <c r="AC20">
-        <v>21.84000015258789</v>
-      </c>
-      <c r="AD20">
-        <v>7.75</v>
-      </c>
-      <c r="AE20">
-        <v>10.333</v>
-      </c>
-      <c r="AF20">
-        <v>1.0333</v>
-      </c>
-      <c r="AG20">
-        <v>23</v>
-      </c>
-      <c r="AH20">
-        <v>502.3200035095215</v>
-      </c>
-      <c r="AI20">
-        <v>5.166500000000001</v>
-      </c>
-      <c r="AJ20">
-        <v>3.22875</v>
-      </c>
-      <c r="AK20">
-        <v>8.395250000000001</v>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AT&amp;T Inc</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>32.12235641479492</v>
-      </c>
-      <c r="D21">
-        <v>29.36555862426758</v>
-      </c>
-      <c r="E21">
-        <v>21.5558910369873</v>
-      </c>
-      <c r="F21">
-        <v>29.51661682128906</v>
-      </c>
-      <c r="G21">
-        <v>21.72205352783203</v>
-      </c>
-      <c r="H21">
-        <v>18.58005905151367</v>
-      </c>
-      <c r="I21">
-        <v>18.40999984741211</v>
-      </c>
-      <c r="J21">
-        <v>16.78000068664551</v>
-      </c>
-      <c r="K21">
-        <v>22.77000045776367</v>
-      </c>
-      <c r="L21">
-        <v>24.84000015258789</v>
-      </c>
-      <c r="M21">
-        <v>25.97999954223633</v>
-      </c>
-      <c r="N21">
-        <v>0.96</v>
-      </c>
-      <c r="O21">
-        <v>1.96</v>
-      </c>
-      <c r="P21">
-        <v>2</v>
-      </c>
-      <c r="Q21">
-        <v>2.04</v>
-      </c>
-      <c r="R21">
-        <v>2.08</v>
-      </c>
-      <c r="S21">
-        <v>2.08</v>
-      </c>
-      <c r="T21">
-        <v>1.354</v>
-      </c>
-      <c r="U21">
-        <v>1.112</v>
-      </c>
-      <c r="V21">
-        <v>1.112</v>
-      </c>
-      <c r="W21">
-        <v>1.112</v>
-      </c>
-      <c r="X21">
-        <v>0.556</v>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>media</t>
-        </is>
-      </c>
-      <c r="Z21">
-        <v>1.487818181818182</v>
-      </c>
-      <c r="AA21">
-        <v>16.366</v>
-      </c>
-      <c r="AB21">
-        <v>32.12235641479492</v>
-      </c>
-      <c r="AC21">
-        <v>25.97999954223633</v>
-      </c>
-      <c r="AD21">
-        <v>-6.142356872558594</v>
-      </c>
-      <c r="AE21">
-        <v>10.22364312744141</v>
-      </c>
-      <c r="AF21">
-        <v>1.022364312744141</v>
-      </c>
-      <c r="AG21">
-        <v>20</v>
-      </c>
-      <c r="AH21">
-        <v>519.5999908447266</v>
-      </c>
-      <c r="AI21">
-        <v>5.111821563720703</v>
-      </c>
-      <c r="AJ21">
-        <v>7.439090909090909</v>
-      </c>
-      <c r="AK21">
-        <v>12.55091247281161</v>
-      </c>
-      <c r="AL21" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>

--- a/ProductionBuild/fullviewfinancials.result.xlsx
+++ b/ProductionBuild/fullviewfinancials.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AL21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -588,7 +588,7 @@
         <v>203.0500030517578</v>
       </c>
       <c r="M2">
-        <v>210.1999969482422</v>
+        <v>204.8200073242188</v>
       </c>
       <c r="N2">
         <v>0.72</v>
@@ -638,31 +638,31 @@
         <v>63.29999923706055</v>
       </c>
       <c r="AC2">
-        <v>210.1999969482422</v>
+        <v>204.8200073242188</v>
       </c>
       <c r="AD2">
-        <v>146.8999977111816</v>
+        <v>141.5200080871582</v>
       </c>
       <c r="AE2">
-        <v>182.2199977111816</v>
+        <v>176.8400080871582</v>
       </c>
       <c r="AF2">
-        <v>18.22199977111816</v>
+        <v>17.68400080871582</v>
       </c>
       <c r="AG2">
         <v>3</v>
       </c>
       <c r="AH2">
-        <v>630.5999908447266</v>
+        <v>614.4600219726563</v>
       </c>
       <c r="AI2">
-        <v>91.10999885559082</v>
+        <v>88.4200040435791</v>
       </c>
       <c r="AJ2">
         <v>16.05454545454545</v>
       </c>
       <c r="AK2">
-        <v>107.1645443101363</v>
+        <v>104.4745494981246</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -673,76 +673,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Swisscom AG</t>
+          <t>NetEase Inc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SCMWY</t>
+          <t>NTES</t>
         </is>
       </c>
       <c r="C3">
-        <v>44.7400016784668</v>
+        <v>43.06800079345703</v>
       </c>
       <c r="D3">
-        <v>53.33000183105469</v>
+        <v>69.01399993896484</v>
       </c>
       <c r="E3">
-        <v>47.95000076293945</v>
+        <v>47.07400131225586</v>
       </c>
       <c r="F3">
-        <v>52.86000061035156</v>
+        <v>61.32799911499023</v>
       </c>
       <c r="G3">
-        <v>53.75</v>
+        <v>95.76999664306641</v>
       </c>
       <c r="H3">
-        <v>56.41999816894531</v>
+        <v>101.7799987792969</v>
       </c>
       <c r="I3">
-        <v>54.91999816894531</v>
+        <v>72.62999725341797</v>
       </c>
       <c r="J3">
-        <v>60.18000030517578</v>
+        <v>93.16000366210938</v>
       </c>
       <c r="K3">
-        <v>56.02999877929688</v>
+        <v>89.20999908447266</v>
       </c>
       <c r="L3">
-        <v>72.79000091552734</v>
+        <v>137.6199951171875</v>
       </c>
       <c r="M3">
-        <v>83.33000183105469</v>
+        <v>109.5400009155273</v>
+      </c>
+      <c r="N3">
+        <v>0.458</v>
       </c>
       <c r="O3">
-        <v>2.181</v>
+        <v>0.728</v>
       </c>
       <c r="P3">
-        <v>2.355</v>
+        <v>0.334</v>
       </c>
       <c r="Q3">
-        <v>2.183</v>
+        <v>1.96</v>
       </c>
       <c r="R3">
-        <v>2.299</v>
+        <v>0.9279999999999999</v>
       </c>
       <c r="S3">
-        <v>2.471</v>
+        <v>0.825</v>
       </c>
       <c r="T3">
-        <v>2.369</v>
+        <v>1.522</v>
       </c>
       <c r="U3">
-        <v>2.343</v>
+        <v>1.755</v>
       </c>
       <c r="V3">
-        <v>2.487</v>
+        <v>2.445</v>
       </c>
       <c r="W3">
-        <v>2.475</v>
+        <v>3.035</v>
       </c>
       <c r="X3">
-        <v>3.378</v>
+        <v>1.16</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -750,40 +753,40 @@
         </is>
       </c>
       <c r="Z3">
-        <v>2.4541</v>
+        <v>1.377272727272727</v>
       </c>
       <c r="AA3">
-        <v>24.541</v>
+        <v>15.15</v>
       </c>
       <c r="AB3">
-        <v>44.7400016784668</v>
+        <v>43.06800079345703</v>
       </c>
       <c r="AC3">
-        <v>83.33000183105469</v>
+        <v>109.5400009155273</v>
       </c>
       <c r="AD3">
-        <v>38.59000015258789</v>
+        <v>66.47200012207031</v>
       </c>
       <c r="AE3">
-        <v>63.13100015258789</v>
+        <v>81.62200012207032</v>
       </c>
       <c r="AF3">
-        <v>6.313100015258788</v>
+        <v>8.162200012207032</v>
       </c>
       <c r="AG3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH3">
-        <v>583.3100128173828</v>
+        <v>547.7000045776367</v>
       </c>
       <c r="AI3">
-        <v>31.56550007629394</v>
+        <v>40.81100006103516</v>
       </c>
       <c r="AJ3">
-        <v>12.2705</v>
+        <v>6.886363636363636</v>
       </c>
       <c r="AK3">
-        <v>43.83600007629394</v>
+        <v>47.69736369739879</v>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
@@ -794,64 +797,76 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK Telecom Co Ltd</t>
+          <t>Swisscom AG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>SCMWY</t>
         </is>
       </c>
       <c r="C4">
-        <v>34.4316291809082</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="D4">
-        <v>45.98023223876953</v>
+        <v>53.33000183105469</v>
       </c>
       <c r="E4">
-        <v>44.15156555175781</v>
+        <v>47.95000076293945</v>
       </c>
       <c r="F4">
-        <v>38.07248687744141</v>
+        <v>52.86000061035156</v>
       </c>
       <c r="G4">
-        <v>40.32949066162109</v>
+        <v>53.75</v>
       </c>
       <c r="H4">
-        <v>26.67000007629395</v>
+        <v>56.41999816894531</v>
       </c>
       <c r="I4">
-        <v>20.59000015258789</v>
+        <v>54.91999816894531</v>
       </c>
       <c r="J4">
-        <v>21.39999961853027</v>
+        <v>60.18000030517578</v>
       </c>
       <c r="K4">
-        <v>21.04000091552734</v>
+        <v>56.02999877929688</v>
       </c>
       <c r="L4">
-        <v>20.53000068664551</v>
+        <v>72.79000091552734</v>
       </c>
       <c r="M4">
-        <v>38.81999969482422</v>
+        <v>84.47000122070313</v>
+      </c>
+      <c r="O4">
+        <v>2.181</v>
+      </c>
+      <c r="P4">
+        <v>2.355</v>
+      </c>
+      <c r="Q4">
+        <v>2.183</v>
       </c>
       <c r="R4">
-        <v>0.15486</v>
+        <v>2.299</v>
       </c>
       <c r="S4">
-        <v>21.034244</v>
+        <v>2.471</v>
       </c>
       <c r="T4">
-        <v>1.402</v>
+        <v>2.369</v>
       </c>
       <c r="U4">
-        <v>1.468</v>
+        <v>2.343</v>
       </c>
       <c r="V4">
-        <v>1.002</v>
+        <v>2.487</v>
       </c>
       <c r="W4">
-        <v>0.738</v>
+        <v>2.475</v>
+      </c>
+      <c r="X4">
+        <v>3.378</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -859,40 +874,40 @@
         </is>
       </c>
       <c r="Z4">
-        <v>4.299850666666666</v>
+        <v>2.4541</v>
       </c>
       <c r="AA4">
-        <v>25.799104</v>
+        <v>24.541</v>
       </c>
       <c r="AB4">
-        <v>34.4316291809082</v>
+        <v>44.7400016784668</v>
       </c>
       <c r="AC4">
-        <v>38.81999969482422</v>
+        <v>84.47000122070313</v>
       </c>
       <c r="AD4">
-        <v>4.388370513916016</v>
+        <v>39.72999954223633</v>
       </c>
       <c r="AE4">
-        <v>30.18747451391601</v>
+        <v>64.27099954223632</v>
       </c>
       <c r="AF4">
-        <v>3.018747451391601</v>
+        <v>6.427099954223633</v>
       </c>
       <c r="AG4">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AH4">
-        <v>504.6599960327148</v>
+        <v>506.8200073242188</v>
       </c>
       <c r="AI4">
-        <v>15.09373725695801</v>
+        <v>32.13549977111816</v>
       </c>
       <c r="AJ4">
-        <v>21.49925333333333</v>
+        <v>12.2705</v>
       </c>
       <c r="AK4">
-        <v>36.59299059029134</v>
+        <v>44.40599977111816</v>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
@@ -903,76 +918,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Elisa Corp</t>
+          <t>SK Telecom Co Ltd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ELMUY</t>
+          <t>SKM</t>
         </is>
       </c>
       <c r="C5">
-        <v>18.5</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="D5">
-        <v>21.14999961853027</v>
+        <v>45.98023223876953</v>
       </c>
       <c r="E5">
-        <v>21</v>
+        <v>44.15156555175781</v>
       </c>
       <c r="F5">
-        <v>26.79999923706055</v>
+        <v>38.07248687744141</v>
       </c>
       <c r="G5">
-        <v>27.85000038146973</v>
+        <v>40.32949066162109</v>
       </c>
       <c r="H5">
-        <v>30.30999946594238</v>
+        <v>26.67000007629395</v>
       </c>
       <c r="I5">
-        <v>23.8700008392334</v>
+        <v>20.59000015258789</v>
       </c>
       <c r="J5">
-        <v>23.06999969482422</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="K5">
-        <v>21.52000045776367</v>
+        <v>21.04000091552734</v>
       </c>
       <c r="L5">
-        <v>23.04500007629395</v>
+        <v>20.53000068664551</v>
       </c>
       <c r="M5">
-        <v>32.75</v>
-      </c>
-      <c r="O5">
-        <v>0.8031</v>
-      </c>
-      <c r="P5">
-        <v>1.005922</v>
-      </c>
-      <c r="Q5">
-        <v>0.987437</v>
+        <v>37.95999908447266</v>
       </c>
       <c r="R5">
-        <v>1.006122</v>
+        <v>0.15486</v>
       </c>
       <c r="S5">
-        <v>1.17429</v>
+        <v>21.034244</v>
       </c>
       <c r="T5">
-        <v>1.109562</v>
+        <v>1.402</v>
       </c>
       <c r="U5">
-        <v>1.17476</v>
+        <v>1.468</v>
       </c>
       <c r="V5">
-        <v>1.212532</v>
+        <v>1.002</v>
       </c>
       <c r="W5">
-        <v>1.345888</v>
-      </c>
-      <c r="X5">
-        <v>0.34533</v>
+        <v>0.738</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -980,40 +983,40 @@
         </is>
       </c>
       <c r="Z5">
-        <v>1.0164943</v>
+        <v>4.299850666666666</v>
       </c>
       <c r="AA5">
-        <v>10.164943</v>
+        <v>25.799104</v>
       </c>
       <c r="AB5">
-        <v>18.5</v>
+        <v>34.4316291809082</v>
       </c>
       <c r="AC5">
-        <v>32.75</v>
+        <v>37.95999908447266</v>
       </c>
       <c r="AD5">
-        <v>14.25</v>
+        <v>3.528369903564453</v>
       </c>
       <c r="AE5">
-        <v>24.414943</v>
+        <v>29.32747390356445</v>
       </c>
       <c r="AF5">
-        <v>2.4414943</v>
+        <v>2.932747390356445</v>
       </c>
       <c r="AG5">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AH5">
-        <v>524</v>
+        <v>531.4399871826172</v>
       </c>
       <c r="AI5">
-        <v>12.2074715</v>
+        <v>14.66373695178222</v>
       </c>
       <c r="AJ5">
-        <v>5.0824715</v>
+        <v>21.49925333333333</v>
       </c>
       <c r="AK5">
-        <v>17.289943</v>
+        <v>36.16299028511555</v>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
@@ -1024,79 +1027,79 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Omnicom Group Inc</t>
+          <t>CAR Group Limited</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>CSXXY</t>
         </is>
       </c>
       <c r="C6">
-        <v>85.11000061035156</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="D6">
-        <v>72.83000183105469</v>
+        <v>22.94000053405762</v>
       </c>
       <c r="E6">
-        <v>73.23999786376953</v>
+        <v>15.3100004196167</v>
       </c>
       <c r="F6">
-        <v>81.01999664306641</v>
+        <v>23.37800025939941</v>
       </c>
       <c r="G6">
-        <v>62.36999893188477</v>
+        <v>30.81999969482422</v>
       </c>
       <c r="H6">
-        <v>73.26999664306641</v>
+        <v>37.70999908447266</v>
       </c>
       <c r="I6">
-        <v>81.56999969482422</v>
+        <v>27.90500068664551</v>
       </c>
       <c r="J6">
-        <v>86.51000213623047</v>
+        <v>42.40999984741211</v>
       </c>
       <c r="K6">
-        <v>86.04000091552734</v>
+        <v>45.5</v>
       </c>
       <c r="L6">
-        <v>80.75</v>
+        <v>40</v>
       </c>
       <c r="M6">
-        <v>78.11000061035156</v>
+        <v>36.77999877929688</v>
       </c>
       <c r="N6">
-        <v>1.65</v>
+        <v>0.3</v>
       </c>
       <c r="O6">
-        <v>2.25</v>
+        <v>0.624</v>
       </c>
       <c r="P6">
-        <v>2.4</v>
+        <v>0.667</v>
       </c>
       <c r="Q6">
-        <v>2.6</v>
+        <v>0.631</v>
       </c>
       <c r="R6">
-        <v>2.6</v>
+        <v>0.6579999999999999</v>
       </c>
       <c r="S6">
-        <v>2.8</v>
+        <v>0.855</v>
       </c>
       <c r="T6">
-        <v>2.8</v>
+        <v>0.708</v>
       </c>
       <c r="U6">
-        <v>2.8</v>
+        <v>0.989</v>
       </c>
       <c r="V6">
-        <v>2.8</v>
+        <v>0.958</v>
       </c>
       <c r="W6">
-        <v>2.9</v>
+        <v>0.483</v>
       </c>
       <c r="X6">
-        <v>0.8</v>
+        <v>0.603</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1104,40 +1107,40 @@
         </is>
       </c>
       <c r="Z6">
-        <v>2.4</v>
+        <v>0.6796363636363636</v>
       </c>
       <c r="AA6">
-        <v>26.4</v>
+        <v>7.476</v>
       </c>
       <c r="AB6">
-        <v>85.11000061035156</v>
+        <v>15.80000019073486</v>
       </c>
       <c r="AC6">
-        <v>78.11000061035156</v>
+        <v>36.77999877929688</v>
       </c>
       <c r="AD6">
-        <v>-7</v>
+        <v>20.97999858856201</v>
       </c>
       <c r="AE6">
-        <v>19.4</v>
+        <v>28.45599858856201</v>
       </c>
       <c r="AF6">
-        <v>1.94</v>
+        <v>2.845599858856201</v>
       </c>
       <c r="AG6">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>546.7700042724609</v>
+        <v>514.9199829101563</v>
       </c>
       <c r="AI6">
-        <v>9.699999999999999</v>
+        <v>14.22799929428101</v>
       </c>
       <c r="AJ6">
-        <v>12</v>
+        <v>3.398181818181818</v>
       </c>
       <c r="AK6">
-        <v>21.7</v>
+        <v>17.62618111246282</v>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
@@ -1148,79 +1151,76 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Verizon Communications Inc</t>
+          <t>Chunghwa Telecom Co Ltd</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>CHT</t>
         </is>
       </c>
       <c r="C7">
-        <v>53.38000106811523</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="D7">
-        <v>52.93000030517578</v>
+        <v>35.43999862670898</v>
       </c>
       <c r="E7">
-        <v>56.22000122070313</v>
+        <v>35.79000091552734</v>
       </c>
       <c r="F7">
-        <v>61.40000152587891</v>
+        <v>36.90000152587891</v>
       </c>
       <c r="G7">
-        <v>58.75</v>
+        <v>38.61999893188477</v>
       </c>
       <c r="H7">
-        <v>51.95999908447266</v>
+        <v>42.20999908447266</v>
       </c>
       <c r="I7">
-        <v>39.40000152587891</v>
+        <v>36.59000015258789</v>
       </c>
       <c r="J7">
-        <v>37.70000076293945</v>
+        <v>39.06999969482422</v>
       </c>
       <c r="K7">
-        <v>39.9900016784668</v>
+        <v>37.65000152587891</v>
       </c>
       <c r="L7">
-        <v>40.72999954223633</v>
+        <v>41.70999908447266</v>
       </c>
       <c r="M7">
-        <v>45.97999954223633</v>
+        <v>43.18000030517578</v>
       </c>
       <c r="N7">
-        <v>1.143</v>
+        <v>1.69</v>
       </c>
       <c r="O7">
-        <v>2.324</v>
+        <v>1.629</v>
       </c>
       <c r="P7">
-        <v>2.373</v>
+        <v>1.59</v>
       </c>
       <c r="Q7">
-        <v>2.424</v>
+        <v>1.443</v>
       </c>
       <c r="R7">
-        <v>2.473</v>
+        <v>1.419</v>
       </c>
       <c r="S7">
-        <v>2.524</v>
+        <v>1.551</v>
       </c>
       <c r="T7">
-        <v>2.573</v>
+        <v>1.591</v>
       </c>
       <c r="U7">
-        <v>2.624</v>
+        <v>1.529</v>
       </c>
       <c r="V7">
-        <v>2.673</v>
+        <v>1.462</v>
       </c>
       <c r="W7">
-        <v>2.724</v>
-      </c>
-      <c r="X7">
-        <v>1.398</v>
+        <v>1.669</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1228,40 +1228,40 @@
         </is>
       </c>
       <c r="Z7">
-        <v>2.295727272727273</v>
+        <v>1.5573</v>
       </c>
       <c r="AA7">
-        <v>25.253</v>
+        <v>15.573</v>
       </c>
       <c r="AB7">
-        <v>53.38000106811523</v>
+        <v>31.54999923706055</v>
       </c>
       <c r="AC7">
-        <v>45.97999954223633</v>
+        <v>43.18000030517578</v>
       </c>
       <c r="AD7">
-        <v>-7.400001525878906</v>
+        <v>11.63000106811523</v>
       </c>
       <c r="AE7">
-        <v>17.85299847412109</v>
+        <v>27.20300106811523</v>
       </c>
       <c r="AF7">
-        <v>1.785299847412109</v>
+        <v>2.720300106811524</v>
       </c>
       <c r="AG7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH7">
-        <v>505.7799949645996</v>
+        <v>518.1600036621094</v>
       </c>
       <c r="AI7">
-        <v>8.926499237060547</v>
+        <v>13.60150053405762</v>
       </c>
       <c r="AJ7">
-        <v>11.47863636363636</v>
+        <v>7.786499999999999</v>
       </c>
       <c r="AK7">
-        <v>20.40513560069691</v>
+        <v>21.38800053405762</v>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
@@ -1272,76 +1272,76 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Orange SA</t>
+          <t>Elisa Corp</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORANY</t>
+          <t>ELMUY</t>
         </is>
       </c>
       <c r="C8">
-        <v>15.14000034332275</v>
+        <v>18.5</v>
       </c>
       <c r="D8">
-        <v>17.39999961853027</v>
+        <v>21.14999961853027</v>
       </c>
       <c r="E8">
-        <v>16.19000053405762</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>14.59000015258789</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="G8">
-        <v>11.85999965667725</v>
+        <v>27.85000038146973</v>
       </c>
       <c r="H8">
-        <v>10.55000019073486</v>
+        <v>30.30999946594238</v>
       </c>
       <c r="I8">
-        <v>9.880000114440918</v>
+        <v>23.8700008392334</v>
       </c>
       <c r="J8">
-        <v>11.43000030517578</v>
+        <v>23.06999969482422</v>
       </c>
       <c r="K8">
-        <v>9.840000152587891</v>
+        <v>21.52000045776367</v>
       </c>
       <c r="L8">
-        <v>16.69000053405762</v>
+        <v>23.04500007629395</v>
       </c>
       <c r="M8">
-        <v>20.45000076293945</v>
-      </c>
-      <c r="N8">
-        <v>0.676</v>
+        <v>32.75</v>
       </c>
       <c r="O8">
-        <v>0.717</v>
+        <v>0.8031</v>
       </c>
       <c r="P8">
-        <v>0.8140000000000001</v>
+        <v>1.005922</v>
       </c>
       <c r="Q8">
-        <v>0.778</v>
+        <v>0.987437</v>
       </c>
       <c r="R8">
-        <v>0.6929999999999999</v>
+        <v>1.006122</v>
       </c>
       <c r="S8">
-        <v>0.944</v>
+        <v>1.17429</v>
       </c>
       <c r="T8">
-        <v>0.733</v>
+        <v>1.109562</v>
       </c>
       <c r="U8">
-        <v>0.759</v>
+        <v>1.17476</v>
       </c>
       <c r="V8">
-        <v>0.769</v>
+        <v>1.212532</v>
       </c>
       <c r="W8">
-        <v>0.516</v>
+        <v>1.345888</v>
+      </c>
+      <c r="X8">
+        <v>0.34533</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1349,40 +1349,40 @@
         </is>
       </c>
       <c r="Z8">
-        <v>0.7399</v>
+        <v>1.0164943</v>
       </c>
       <c r="AA8">
-        <v>7.399</v>
+        <v>10.164943</v>
       </c>
       <c r="AB8">
-        <v>15.14000034332275</v>
+        <v>18.5</v>
       </c>
       <c r="AC8">
-        <v>20.45000076293945</v>
+        <v>32.75</v>
       </c>
       <c r="AD8">
-        <v>5.310000419616699</v>
+        <v>14.25</v>
       </c>
       <c r="AE8">
-        <v>12.7090004196167</v>
+        <v>24.414943</v>
       </c>
       <c r="AF8">
-        <v>1.27090004196167</v>
+        <v>2.4414943</v>
       </c>
       <c r="AG8">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AH8">
-        <v>511.2500190734863</v>
+        <v>524</v>
       </c>
       <c r="AI8">
-        <v>6.35450020980835</v>
+        <v>12.2074715</v>
       </c>
       <c r="AJ8">
-        <v>3.6995</v>
+        <v>5.0824715</v>
       </c>
       <c r="AK8">
-        <v>10.05400020980835</v>
+        <v>17.289943</v>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
@@ -1393,76 +1393,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Telenor ASA</t>
+          <t>Deutsche Telekom AG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TELNY</t>
+          <t>DTEGY</t>
         </is>
       </c>
       <c r="C9">
-        <v>14.92000007629395</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="D9">
-        <v>21.38999938964844</v>
+        <v>17.65999984741211</v>
       </c>
       <c r="E9">
-        <v>19.3700008392334</v>
+        <v>16.97999954223633</v>
       </c>
       <c r="F9">
-        <v>17.90999984741211</v>
+        <v>16.29000091552734</v>
       </c>
       <c r="G9">
-        <v>17</v>
+        <v>18.27000045776367</v>
       </c>
       <c r="H9">
-        <v>15.68000030517578</v>
+        <v>18.51000022888184</v>
       </c>
       <c r="I9">
-        <v>9.289999961853027</v>
+        <v>19.97999954223633</v>
       </c>
       <c r="J9">
-        <v>11.48999977111816</v>
+        <v>24.1299991607666</v>
       </c>
       <c r="K9">
-        <v>11.14000034332275</v>
+        <v>29.85000038146973</v>
       </c>
       <c r="L9">
-        <v>14.60999965667725</v>
+        <v>32.70000076293945</v>
       </c>
       <c r="M9">
-        <v>17.45000076293945</v>
+        <v>31.98999977111816</v>
       </c>
       <c r="N9">
-        <v>0.897</v>
+        <v>0.606</v>
       </c>
       <c r="O9">
-        <v>0.9470000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="P9">
-        <v>1.547</v>
+        <v>0.798</v>
       </c>
       <c r="Q9">
-        <v>0.966</v>
+        <v>0.784</v>
       </c>
       <c r="R9">
-        <v>0.9430000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="S9">
-        <v>1.064</v>
+        <v>0.715</v>
       </c>
       <c r="T9">
-        <v>1.018</v>
+        <v>0.7</v>
       </c>
       <c r="U9">
-        <v>0.887</v>
+        <v>0.745</v>
       </c>
       <c r="V9">
-        <v>0.897</v>
+        <v>0.835</v>
       </c>
       <c r="W9">
-        <v>0.9019999999999999</v>
+        <v>1.023</v>
+      </c>
+      <c r="X9">
+        <v>1.159</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1470,40 +1473,40 @@
         </is>
       </c>
       <c r="Z9">
-        <v>1.0068</v>
+        <v>0.7890909090909091</v>
       </c>
       <c r="AA9">
-        <v>10.068</v>
+        <v>8.68</v>
       </c>
       <c r="AB9">
-        <v>14.92000007629395</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="AC9">
-        <v>17.45000076293945</v>
+        <v>31.98999977111816</v>
       </c>
       <c r="AD9">
-        <v>2.530000686645508</v>
+        <v>14.88999938964844</v>
       </c>
       <c r="AE9">
-        <v>12.59800068664551</v>
+        <v>23.56999938964844</v>
       </c>
       <c r="AF9">
-        <v>1.259800068664551</v>
+        <v>2.356999938964844</v>
       </c>
       <c r="AG9">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="AH9">
-        <v>506.0500221252441</v>
+        <v>511.8399963378906</v>
       </c>
       <c r="AI9">
-        <v>6.299000343322754</v>
+        <v>11.78499969482422</v>
       </c>
       <c r="AJ9">
-        <v>5.034000000000001</v>
+        <v>3.945454545454545</v>
       </c>
       <c r="AK9">
-        <v>11.33300034332276</v>
+        <v>15.73045424027876</v>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
@@ -1514,76 +1517,76 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Publicis Groupe SA</t>
+          <t>Singapore Telecommunications Ltd</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PUBGY</t>
+          <t>SGAPY</t>
         </is>
       </c>
       <c r="C10">
-        <v>17.20000076293945</v>
+        <v>24.94000053405762</v>
       </c>
       <c r="D10">
-        <v>16.98999977111816</v>
+        <v>26.64999961853027</v>
       </c>
       <c r="E10">
-        <v>14.15999984741211</v>
+        <v>21.5</v>
       </c>
       <c r="F10">
-        <v>11.31999969482422</v>
+        <v>25.05999946594238</v>
       </c>
       <c r="G10">
-        <v>12.34000015258789</v>
+        <v>17.39999961853027</v>
       </c>
       <c r="H10">
-        <v>16.89999961853027</v>
+        <v>17.19000053405762</v>
       </c>
       <c r="I10">
-        <v>15.86999988555908</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="J10">
-        <v>23.18000030517578</v>
+        <v>18.69000053405762</v>
       </c>
       <c r="K10">
-        <v>26.53000068664551</v>
+        <v>22.53000068664551</v>
       </c>
       <c r="L10">
-        <v>25.8799991607666</v>
+        <v>35.40999984741211</v>
       </c>
       <c r="M10">
-        <v>22.86000061035156</v>
+        <v>36.7400016784668</v>
       </c>
       <c r="N10">
-        <v>0.45</v>
+        <v>1.274</v>
       </c>
       <c r="O10">
-        <v>0.507</v>
+        <v>1.28</v>
       </c>
       <c r="P10">
-        <v>0.588</v>
+        <v>1.293</v>
       </c>
       <c r="Q10">
-        <v>0.593</v>
+        <v>1.278</v>
       </c>
       <c r="R10">
-        <v>0.343</v>
+        <v>0.763</v>
       </c>
       <c r="S10">
-        <v>0.604</v>
+        <v>0.512</v>
       </c>
       <c r="T10">
-        <v>0.642</v>
+        <v>0.861</v>
       </c>
       <c r="U10">
-        <v>0.776</v>
+        <v>0.959</v>
       </c>
       <c r="V10">
-        <v>0.923</v>
+        <v>1.249</v>
       </c>
       <c r="W10">
-        <v>1.059</v>
+        <v>0.773</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1591,40 +1594,40 @@
         </is>
       </c>
       <c r="Z10">
-        <v>0.6485</v>
+        <v>1.0242</v>
       </c>
       <c r="AA10">
-        <v>6.485</v>
+        <v>10.242</v>
       </c>
       <c r="AB10">
-        <v>17.20000076293945</v>
+        <v>24.94000053405762</v>
       </c>
       <c r="AC10">
-        <v>22.86000061035156</v>
+        <v>36.7400016784668</v>
       </c>
       <c r="AD10">
-        <v>5.659999847412109</v>
+        <v>11.80000114440918</v>
       </c>
       <c r="AE10">
-        <v>12.14499984741211</v>
+        <v>22.04200114440918</v>
       </c>
       <c r="AF10">
-        <v>1.214499984741211</v>
+        <v>2.204200114440918</v>
       </c>
       <c r="AG10">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AH10">
-        <v>502.9200134277344</v>
+        <v>514.3600234985352</v>
       </c>
       <c r="AI10">
-        <v>6.072499923706054</v>
+        <v>11.02100057220459</v>
       </c>
       <c r="AJ10">
-        <v>3.2425</v>
+        <v>5.121</v>
       </c>
       <c r="AK10">
-        <v>9.314999923706054</v>
+        <v>16.14200057220459</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
@@ -1635,79 +1638,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PLDT Inc</t>
+          <t>Match Group Inc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MTCH</t>
         </is>
       </c>
       <c r="C11">
-        <v>27.54999923706055</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="D11">
-        <v>30.07999992370605</v>
+        <v>31.30999946594238</v>
       </c>
       <c r="E11">
-        <v>21.3799991607666</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="F11">
-        <v>19.98999977111816</v>
+        <v>82.11000061035156</v>
       </c>
       <c r="G11">
-        <v>27.90999984741211</v>
+        <v>151.1900024414063</v>
       </c>
       <c r="H11">
-        <v>35.72000122070313</v>
+        <v>132.25</v>
       </c>
       <c r="I11">
-        <v>22.79999923706055</v>
+        <v>41.4900016784668</v>
       </c>
       <c r="J11">
-        <v>23.43000030517578</v>
+        <v>36.5</v>
       </c>
       <c r="K11">
-        <v>22.14999961853027</v>
+        <v>32.70999908447266</v>
       </c>
       <c r="L11">
-        <v>21.73999977111816</v>
+        <v>32.29000091552734</v>
       </c>
       <c r="M11">
-        <v>20.94000053405762</v>
-      </c>
-      <c r="N11">
-        <v>1.042</v>
-      </c>
-      <c r="O11">
-        <v>1.497</v>
+        <v>35.65999984741211</v>
       </c>
       <c r="P11">
-        <v>0.534</v>
-      </c>
-      <c r="Q11">
-        <v>1.37</v>
-      </c>
-      <c r="R11">
-        <v>1.544</v>
-      </c>
-      <c r="S11">
-        <v>1.669</v>
-      </c>
-      <c r="T11">
-        <v>2.161</v>
-      </c>
-      <c r="U11">
-        <v>1.961</v>
-      </c>
-      <c r="V11">
-        <v>1.703</v>
+        <v>2</v>
       </c>
       <c r="W11">
-        <v>0.821</v>
+        <v>0.76</v>
       </c>
       <c r="X11">
-        <v>0.798</v>
+        <v>0.39</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1715,40 +1694,40 @@
         </is>
       </c>
       <c r="Z11">
-        <v>1.372727272727273</v>
+        <v>1.05</v>
       </c>
       <c r="AA11">
-        <v>15.1</v>
+        <v>3.15</v>
       </c>
       <c r="AB11">
-        <v>27.54999923706055</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="AC11">
-        <v>20.94000053405762</v>
+        <v>35.65999984741211</v>
       </c>
       <c r="AD11">
-        <v>-6.60999870300293</v>
+        <v>18.55999946594238</v>
       </c>
       <c r="AE11">
-        <v>8.49000129699707</v>
+        <v>21.70999946594238</v>
       </c>
       <c r="AF11">
-        <v>0.849000129699707</v>
+        <v>2.170999946594238</v>
       </c>
       <c r="AG11">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="AH11">
-        <v>502.5600128173828</v>
+        <v>534.8999977111816</v>
       </c>
       <c r="AI11">
-        <v>4.245000648498535</v>
+        <v>10.85499973297119</v>
       </c>
       <c r="AJ11">
-        <v>6.863636363636364</v>
+        <v>5.25</v>
       </c>
       <c r="AK11">
-        <v>11.1086370121349</v>
+        <v>16.10499973297119</v>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
@@ -1759,79 +1738,79 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Comcast Corp</t>
+          <t>Verizon Communications Inc</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="C12">
-        <v>32.35707473754883</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="D12">
-        <v>37.5351448059082</v>
+        <v>52.93000030517578</v>
       </c>
       <c r="E12">
-        <v>31.91190338134766</v>
+        <v>56.22000122070313</v>
       </c>
       <c r="F12">
-        <v>42.14620590209961</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="G12">
-        <v>49.10965347290039</v>
+        <v>58.75</v>
       </c>
       <c r="H12">
-        <v>47.16963577270508</v>
+        <v>51.95999908447266</v>
       </c>
       <c r="I12">
-        <v>32.77413177490234</v>
+        <v>39.40000152587891</v>
       </c>
       <c r="J12">
-        <v>41.09653091430664</v>
+        <v>37.70000076293945</v>
       </c>
       <c r="K12">
-        <v>35.17338180541992</v>
+        <v>39.9900016784668</v>
       </c>
       <c r="L12">
-        <v>28.01312065124512</v>
+        <v>40.72999954223633</v>
       </c>
       <c r="M12">
-        <v>29.3700008392334</v>
+        <v>47.22000122070313</v>
       </c>
       <c r="N12">
-        <v>0.386598</v>
+        <v>1.143</v>
       </c>
       <c r="O12">
-        <v>0.444237</v>
+        <v>2.324</v>
       </c>
       <c r="P12">
-        <v>0.860355</v>
+        <v>2.373</v>
       </c>
       <c r="Q12">
-        <v>0.5904389999999999</v>
+        <v>2.424</v>
       </c>
       <c r="R12">
-        <v>0.843487</v>
+        <v>2.473</v>
       </c>
       <c r="S12">
-        <v>0.9184640000000001</v>
+        <v>2.524</v>
       </c>
       <c r="T12">
-        <v>0.99344</v>
+        <v>2.573</v>
       </c>
       <c r="U12">
-        <v>1.068416</v>
+        <v>2.624</v>
       </c>
       <c r="V12">
-        <v>1.143392</v>
+        <v>2.673</v>
       </c>
       <c r="W12">
-        <v>1.218368</v>
+        <v>2.724</v>
       </c>
       <c r="X12">
-        <v>0.66</v>
+        <v>1.398</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1839,40 +1818,40 @@
         </is>
       </c>
       <c r="Z12">
-        <v>0.8297450909090909</v>
+        <v>2.295727272727273</v>
       </c>
       <c r="AA12">
-        <v>9.127196</v>
+        <v>25.253</v>
       </c>
       <c r="AB12">
-        <v>32.35707473754883</v>
+        <v>53.38000106811523</v>
       </c>
       <c r="AC12">
-        <v>29.3700008392334</v>
+        <v>47.22000122070313</v>
       </c>
       <c r="AD12">
-        <v>-2.98707389831543</v>
+        <v>-6.159999847412109</v>
       </c>
       <c r="AE12">
-        <v>6.14012210168457</v>
+        <v>19.09300015258789</v>
       </c>
       <c r="AF12">
-        <v>0.614012210168457</v>
+        <v>1.909300015258789</v>
       </c>
       <c r="AG12">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AH12">
-        <v>528.6600151062012</v>
+        <v>519.4200134277344</v>
       </c>
       <c r="AI12">
-        <v>3.070061050842285</v>
+        <v>9.546500076293945</v>
       </c>
       <c r="AJ12">
-        <v>4.148725454545454</v>
+        <v>11.47863636363636</v>
       </c>
       <c r="AK12">
-        <v>7.218786505387739</v>
+        <v>21.02513643993031</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
@@ -1883,79 +1862,79 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCE Inc.</t>
+          <t>Omnicom Group Inc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BCE</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="C13">
-        <v>43.2400016784668</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="D13">
-        <v>48.0099983215332</v>
+        <v>72.83000183105469</v>
       </c>
       <c r="E13">
-        <v>39.52999877929688</v>
+        <v>73.23999786376953</v>
       </c>
       <c r="F13">
-        <v>46.34999847412109</v>
+        <v>81.01999664306641</v>
       </c>
       <c r="G13">
-        <v>42.79999923706055</v>
+        <v>62.36999893188477</v>
       </c>
       <c r="H13">
-        <v>52.04000091552734</v>
+        <v>73.26999664306641</v>
       </c>
       <c r="I13">
-        <v>43.95000076293945</v>
+        <v>81.56999969482422</v>
       </c>
       <c r="J13">
-        <v>39.38000106811523</v>
+        <v>86.51000213623047</v>
       </c>
       <c r="K13">
-        <v>23.18000030517578</v>
+        <v>86.04000091552734</v>
       </c>
       <c r="L13">
-        <v>23.81999969482422</v>
+        <v>80.75</v>
       </c>
       <c r="M13">
-        <v>23.72999954223633</v>
+        <v>76.81999969482422</v>
       </c>
       <c r="N13">
-        <v>1.577</v>
+        <v>1.65</v>
       </c>
       <c r="O13">
-        <v>2.221</v>
+        <v>2.25</v>
       </c>
       <c r="P13">
-        <v>1.744</v>
+        <v>2.4</v>
       </c>
       <c r="Q13">
-        <v>2.391</v>
+        <v>2.6</v>
       </c>
       <c r="R13">
-        <v>2.493</v>
+        <v>2.6</v>
       </c>
       <c r="S13">
-        <v>2.793</v>
+        <v>2.8</v>
       </c>
       <c r="T13">
-        <v>2.814</v>
+        <v>2.8</v>
       </c>
       <c r="U13">
-        <v>2.862</v>
+        <v>2.8</v>
       </c>
       <c r="V13">
-        <v>2.896</v>
+        <v>2.8</v>
       </c>
       <c r="W13">
-        <v>1.663</v>
+        <v>2.9</v>
       </c>
       <c r="X13">
-        <v>0.319</v>
+        <v>0.8</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1963,40 +1942,40 @@
         </is>
       </c>
       <c r="Z13">
-        <v>2.161181818181818</v>
+        <v>2.4</v>
       </c>
       <c r="AA13">
-        <v>23.773</v>
+        <v>26.4</v>
       </c>
       <c r="AB13">
-        <v>43.2400016784668</v>
+        <v>85.11000061035156</v>
       </c>
       <c r="AC13">
-        <v>23.72999954223633</v>
+        <v>76.81999969482422</v>
       </c>
       <c r="AD13">
-        <v>-19.51000213623047</v>
+        <v>-8.290000915527344</v>
       </c>
       <c r="AE13">
-        <v>4.262997863769531</v>
+        <v>18.10999908447265</v>
       </c>
       <c r="AF13">
-        <v>0.4262997863769531</v>
+        <v>1.810999908447265</v>
       </c>
       <c r="AG13">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="AH13">
-        <v>522.0599899291992</v>
+        <v>537.7399978637695</v>
       </c>
       <c r="AI13">
-        <v>2.131498931884765</v>
+        <v>9.054999542236327</v>
       </c>
       <c r="AJ13">
-        <v>10.80590909090909</v>
+        <v>12</v>
       </c>
       <c r="AK13">
-        <v>12.93740802279386</v>
+        <v>21.05499954223633</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
@@ -2007,76 +1986,76 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Perusahaan Perseroan (Persero) PT Telekomunikasi I</t>
+          <t>America Movil SAB de CV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>AMX</t>
         </is>
       </c>
       <c r="C14">
-        <v>29.15999984741211</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="D14">
-        <v>32.22000122070313</v>
+        <v>17.14999961853027</v>
       </c>
       <c r="E14">
-        <v>26.20999908447266</v>
+        <v>14.25</v>
       </c>
       <c r="F14">
-        <v>28.5</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>23.52000045776367</v>
+        <v>14.53999996185303</v>
       </c>
       <c r="H14">
-        <v>28.98999977111816</v>
+        <v>21.11000061035156</v>
       </c>
       <c r="I14">
-        <v>23.85000038146973</v>
+        <v>18.20000076293945</v>
       </c>
       <c r="J14">
-        <v>25.76000022888184</v>
+        <v>18.52000045776367</v>
       </c>
       <c r="K14">
-        <v>16.45000076293945</v>
+        <v>14.3100004196167</v>
       </c>
       <c r="L14">
-        <v>21.04999923706055</v>
+        <v>20.67000007629395</v>
       </c>
       <c r="M14">
-        <v>17.68000030517578</v>
+        <v>26.04000091552734</v>
       </c>
       <c r="N14">
-        <v>0.8615</v>
+        <v>0.302</v>
       </c>
       <c r="O14">
-        <v>0.881</v>
+        <v>0.327</v>
       </c>
       <c r="P14">
-        <v>1.203</v>
+        <v>0.319</v>
       </c>
       <c r="Q14">
-        <v>1.137</v>
+        <v>0.366</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>0.352</v>
       </c>
       <c r="S14">
-        <v>1.177</v>
+        <v>0.397</v>
       </c>
       <c r="T14">
-        <v>1.039</v>
+        <v>0.802</v>
       </c>
       <c r="U14">
-        <v>1.13</v>
+        <v>0.525</v>
       </c>
       <c r="V14">
-        <v>1.112</v>
+        <v>0.506</v>
       </c>
       <c r="W14">
-        <v>1.287</v>
+        <v>0.277</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -2084,40 +2063,40 @@
         </is>
       </c>
       <c r="Z14">
-        <v>1.09075</v>
+        <v>0.4173</v>
       </c>
       <c r="AA14">
-        <v>10.9075</v>
+        <v>4.173</v>
       </c>
       <c r="AB14">
-        <v>29.15999984741211</v>
+        <v>12.56999969482422</v>
       </c>
       <c r="AC14">
-        <v>17.68000030517578</v>
+        <v>26.04000091552734</v>
       </c>
       <c r="AD14">
-        <v>-11.47999954223633</v>
+        <v>13.47000122070313</v>
       </c>
       <c r="AE14">
-        <v>-0.5724995422363275</v>
+        <v>17.64300122070313</v>
       </c>
       <c r="AF14">
-        <v>-0.05724995422363275</v>
+        <v>1.764300122070313</v>
       </c>
       <c r="AG14">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AH14">
-        <v>512.7200088500977</v>
+        <v>520.8000183105469</v>
       </c>
       <c r="AI14">
-        <v>-0.2862497711181637</v>
+        <v>8.821500610351563</v>
       </c>
       <c r="AJ14">
-        <v>5.45375</v>
+        <v>2.0865</v>
       </c>
       <c r="AK14">
-        <v>5.167500228881837</v>
+        <v>10.90800061035156</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
@@ -2128,79 +2107,79 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sirius XM Holdings Inc</t>
+          <t>Rogers Communications Inc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SIRI</t>
+          <t>RCI</t>
         </is>
       </c>
       <c r="C15">
-        <v>44.5</v>
+        <v>38.58000183105469</v>
       </c>
       <c r="D15">
-        <v>53.59999847412109</v>
+        <v>50.93000030517578</v>
       </c>
       <c r="E15">
-        <v>57.09999847412109</v>
+        <v>51.2599983215332</v>
       </c>
       <c r="F15">
-        <v>71.5</v>
+        <v>49.66999816894531</v>
       </c>
       <c r="G15">
-        <v>63.70000076293945</v>
+        <v>46.59000015258789</v>
       </c>
       <c r="H15">
-        <v>63.5</v>
+        <v>47.63000106811523</v>
       </c>
       <c r="I15">
-        <v>58.40000152587891</v>
+        <v>46.84000015258789</v>
       </c>
       <c r="J15">
-        <v>54.70000076293945</v>
+        <v>46.81000137329102</v>
       </c>
       <c r="K15">
-        <v>22.79999923706055</v>
+        <v>30.72999954223633</v>
       </c>
       <c r="L15">
-        <v>20</v>
+        <v>37.72999954223633</v>
       </c>
       <c r="M15">
-        <v>28.05999946594238</v>
+        <v>37.34999847412109</v>
       </c>
       <c r="N15">
-        <v>0.1</v>
+        <v>1.114</v>
       </c>
       <c r="O15">
-        <v>0.41</v>
+        <v>1.478</v>
       </c>
       <c r="P15">
-        <v>0.45</v>
+        <v>1.471</v>
       </c>
       <c r="Q15">
-        <v>0.49</v>
+        <v>1.503</v>
       </c>
       <c r="R15">
-        <v>0.54</v>
+        <v>1.519</v>
       </c>
       <c r="S15">
-        <v>0.6699999999999999</v>
+        <v>1.598</v>
       </c>
       <c r="T15">
-        <v>3.4</v>
+        <v>1.533</v>
       </c>
       <c r="U15">
-        <v>0.99</v>
+        <v>1.471</v>
       </c>
       <c r="V15">
-        <v>1.08</v>
+        <v>1.456</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.075</v>
       </c>
       <c r="X15">
-        <v>0.27</v>
+        <v>0.368</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -2208,40 +2187,40 @@
         </is>
       </c>
       <c r="Z15">
-        <v>0.8618181818181818</v>
+        <v>1.326</v>
       </c>
       <c r="AA15">
-        <v>9.48</v>
+        <v>14.586</v>
       </c>
       <c r="AB15">
-        <v>44.5</v>
+        <v>38.58000183105469</v>
       </c>
       <c r="AC15">
-        <v>28.05999946594238</v>
+        <v>37.34999847412109</v>
       </c>
       <c r="AD15">
-        <v>-16.44000053405762</v>
+        <v>-1.230003356933594</v>
       </c>
       <c r="AE15">
-        <v>-6.960000534057617</v>
+        <v>13.35599664306641</v>
       </c>
       <c r="AF15">
-        <v>-0.6960000534057617</v>
+        <v>1.335599664306641</v>
       </c>
       <c r="AG15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AH15">
-        <v>505.0799903869629</v>
+        <v>522.8999786376953</v>
       </c>
       <c r="AI15">
-        <v>-3.480000267028808</v>
+        <v>6.677998321533202</v>
       </c>
       <c r="AJ15">
-        <v>4.309090909090909</v>
+        <v>6.630000000000001</v>
       </c>
       <c r="AK15">
-        <v>0.8290906420621003</v>
+        <v>13.3079983215332</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
@@ -2252,46 +2231,76 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Millicom International Cellular SA</t>
+          <t>Orange SA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TIGO</t>
-        </is>
+          <t>ORANY</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>15.14000034332275</v>
+      </c>
+      <c r="D16">
+        <v>17.39999961853027</v>
+      </c>
+      <c r="E16">
+        <v>16.19000053405762</v>
       </c>
       <c r="F16">
-        <v>48.22999954223633</v>
+        <v>14.59000015258789</v>
       </c>
       <c r="G16">
-        <v>38.77999877929688</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="H16">
-        <v>28.45000076293945</v>
+        <v>10.55000019073486</v>
       </c>
       <c r="I16">
-        <v>12.63000011444092</v>
+        <v>9.880000114440918</v>
       </c>
       <c r="J16">
-        <v>18</v>
+        <v>11.43000030517578</v>
       </c>
       <c r="K16">
-        <v>25.01000022888184</v>
+        <v>9.840000152587891</v>
       </c>
       <c r="L16">
-        <v>55.43999862670898</v>
+        <v>16.69000053405762</v>
       </c>
       <c r="M16">
-        <v>83.15000152587891</v>
+        <v>21</v>
+      </c>
+      <c r="N16">
+        <v>0.676</v>
+      </c>
+      <c r="O16">
+        <v>0.717</v>
+      </c>
+      <c r="P16">
+        <v>0.8140000000000001</v>
       </c>
       <c r="Q16">
-        <v>2.64</v>
+        <v>0.778</v>
+      </c>
+      <c r="R16">
+        <v>0.6929999999999999</v>
+      </c>
+      <c r="S16">
+        <v>0.944</v>
+      </c>
+      <c r="T16">
+        <v>0.733</v>
+      </c>
+      <c r="U16">
+        <v>0.759</v>
+      </c>
+      <c r="V16">
+        <v>0.769</v>
       </c>
       <c r="W16">
-        <v>4.5</v>
-      </c>
-      <c r="X16">
-        <v>2.75</v>
+        <v>0.516</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -2299,24 +2308,626 @@
         </is>
       </c>
       <c r="Z16">
-        <v>3.296666666666667</v>
+        <v>0.7399</v>
       </c>
       <c r="AA16">
-        <v>9.890000000000001</v>
+        <v>7.399</v>
+      </c>
+      <c r="AB16">
+        <v>15.14000034332275</v>
       </c>
       <c r="AC16">
-        <v>83.15000152587891</v>
+        <v>21</v>
+      </c>
+      <c r="AD16">
+        <v>5.859999656677246</v>
+      </c>
+      <c r="AE16">
+        <v>13.25899965667725</v>
+      </c>
+      <c r="AF16">
+        <v>1.325899965667725</v>
       </c>
       <c r="AG16">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AH16">
-        <v>582.0500106811523</v>
+        <v>504</v>
+      </c>
+      <c r="AI16">
+        <v>6.629499828338624</v>
       </c>
       <c r="AJ16">
-        <v>16.48333333333333</v>
+        <v>3.6995</v>
+      </c>
+      <c r="AK16">
+        <v>10.32899982833862</v>
       </c>
       <c r="AL16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Telenor ASA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TELNY</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>14.92000007629395</v>
+      </c>
+      <c r="D17">
+        <v>21.38999938964844</v>
+      </c>
+      <c r="E17">
+        <v>19.3700008392334</v>
+      </c>
+      <c r="F17">
+        <v>17.90999984741211</v>
+      </c>
+      <c r="G17">
+        <v>17</v>
+      </c>
+      <c r="H17">
+        <v>15.68000030517578</v>
+      </c>
+      <c r="I17">
+        <v>9.289999961853027</v>
+      </c>
+      <c r="J17">
+        <v>11.48999977111816</v>
+      </c>
+      <c r="K17">
+        <v>11.14000034332275</v>
+      </c>
+      <c r="L17">
+        <v>14.60999965667725</v>
+      </c>
+      <c r="M17">
+        <v>17.45000076293945</v>
+      </c>
+      <c r="N17">
+        <v>0.897</v>
+      </c>
+      <c r="O17">
+        <v>0.9470000000000001</v>
+      </c>
+      <c r="P17">
+        <v>1.547</v>
+      </c>
+      <c r="Q17">
+        <v>0.966</v>
+      </c>
+      <c r="R17">
+        <v>0.9430000000000001</v>
+      </c>
+      <c r="S17">
+        <v>1.064</v>
+      </c>
+      <c r="T17">
+        <v>1.018</v>
+      </c>
+      <c r="U17">
+        <v>0.887</v>
+      </c>
+      <c r="V17">
+        <v>0.897</v>
+      </c>
+      <c r="W17">
+        <v>0.9019999999999999</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="Z17">
+        <v>1.0068</v>
+      </c>
+      <c r="AA17">
+        <v>10.068</v>
+      </c>
+      <c r="AB17">
+        <v>14.92000007629395</v>
+      </c>
+      <c r="AC17">
+        <v>17.45000076293945</v>
+      </c>
+      <c r="AD17">
+        <v>2.530000686645508</v>
+      </c>
+      <c r="AE17">
+        <v>12.59800068664551</v>
+      </c>
+      <c r="AF17">
+        <v>1.259800068664551</v>
+      </c>
+      <c r="AG17">
+        <v>29</v>
+      </c>
+      <c r="AH17">
+        <v>506.0500221252441</v>
+      </c>
+      <c r="AI17">
+        <v>6.299000343322754</v>
+      </c>
+      <c r="AJ17">
+        <v>5.034000000000001</v>
+      </c>
+      <c r="AK17">
+        <v>11.33300034332276</v>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Publicis Groupe SA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PUBGY</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>17.20000076293945</v>
+      </c>
+      <c r="D18">
+        <v>16.98999977111816</v>
+      </c>
+      <c r="E18">
+        <v>14.15999984741211</v>
+      </c>
+      <c r="F18">
+        <v>11.31999969482422</v>
+      </c>
+      <c r="G18">
+        <v>12.34000015258789</v>
+      </c>
+      <c r="H18">
+        <v>16.89999961853027</v>
+      </c>
+      <c r="I18">
+        <v>15.86999988555908</v>
+      </c>
+      <c r="J18">
+        <v>23.18000030517578</v>
+      </c>
+      <c r="K18">
+        <v>26.53000068664551</v>
+      </c>
+      <c r="L18">
+        <v>25.8799991607666</v>
+      </c>
+      <c r="M18">
+        <v>22.51000022888184</v>
+      </c>
+      <c r="N18">
+        <v>0.45</v>
+      </c>
+      <c r="O18">
+        <v>0.507</v>
+      </c>
+      <c r="P18">
+        <v>0.588</v>
+      </c>
+      <c r="Q18">
+        <v>0.593</v>
+      </c>
+      <c r="R18">
+        <v>0.343</v>
+      </c>
+      <c r="S18">
+        <v>0.604</v>
+      </c>
+      <c r="T18">
+        <v>0.642</v>
+      </c>
+      <c r="U18">
+        <v>0.776</v>
+      </c>
+      <c r="V18">
+        <v>0.923</v>
+      </c>
+      <c r="W18">
+        <v>1.059</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="Z18">
+        <v>0.6485</v>
+      </c>
+      <c r="AA18">
+        <v>6.485</v>
+      </c>
+      <c r="AB18">
+        <v>17.20000076293945</v>
+      </c>
+      <c r="AC18">
+        <v>22.51000022888184</v>
+      </c>
+      <c r="AD18">
+        <v>5.309999465942383</v>
+      </c>
+      <c r="AE18">
+        <v>11.79499946594238</v>
+      </c>
+      <c r="AF18">
+        <v>1.179499946594238</v>
+      </c>
+      <c r="AG18">
+        <v>23</v>
+      </c>
+      <c r="AH18">
+        <v>517.7300052642822</v>
+      </c>
+      <c r="AI18">
+        <v>5.897499732971191</v>
+      </c>
+      <c r="AJ18">
+        <v>3.2425</v>
+      </c>
+      <c r="AK18">
+        <v>9.139999732971191</v>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AT&amp;T Inc</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>32.12235641479492</v>
+      </c>
+      <c r="D19">
+        <v>29.36555862426758</v>
+      </c>
+      <c r="E19">
+        <v>21.5558910369873</v>
+      </c>
+      <c r="F19">
+        <v>29.51661682128906</v>
+      </c>
+      <c r="G19">
+        <v>21.72205352783203</v>
+      </c>
+      <c r="H19">
+        <v>18.58005905151367</v>
+      </c>
+      <c r="I19">
+        <v>18.40999984741211</v>
+      </c>
+      <c r="J19">
+        <v>16.78000068664551</v>
+      </c>
+      <c r="K19">
+        <v>22.77000045776367</v>
+      </c>
+      <c r="L19">
+        <v>24.84000015258789</v>
+      </c>
+      <c r="M19">
+        <v>26.61000061035156</v>
+      </c>
+      <c r="N19">
+        <v>0.96</v>
+      </c>
+      <c r="O19">
+        <v>1.96</v>
+      </c>
+      <c r="P19">
+        <v>2</v>
+      </c>
+      <c r="Q19">
+        <v>2.04</v>
+      </c>
+      <c r="R19">
+        <v>2.08</v>
+      </c>
+      <c r="S19">
+        <v>2.08</v>
+      </c>
+      <c r="T19">
+        <v>1.354</v>
+      </c>
+      <c r="U19">
+        <v>1.112</v>
+      </c>
+      <c r="V19">
+        <v>1.112</v>
+      </c>
+      <c r="W19">
+        <v>1.112</v>
+      </c>
+      <c r="X19">
+        <v>0.556</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="Z19">
+        <v>1.487818181818182</v>
+      </c>
+      <c r="AA19">
+        <v>16.366</v>
+      </c>
+      <c r="AB19">
+        <v>32.12235641479492</v>
+      </c>
+      <c r="AC19">
+        <v>26.61000061035156</v>
+      </c>
+      <c r="AD19">
+        <v>-5.512355804443359</v>
+      </c>
+      <c r="AE19">
+        <v>10.85364419555664</v>
+      </c>
+      <c r="AF19">
+        <v>1.085364419555664</v>
+      </c>
+      <c r="AG19">
+        <v>19</v>
+      </c>
+      <c r="AH19">
+        <v>505.5900115966797</v>
+      </c>
+      <c r="AI19">
+        <v>5.42682209777832</v>
+      </c>
+      <c r="AJ19">
+        <v>7.439090909090909</v>
+      </c>
+      <c r="AK19">
+        <v>12.86591300686923</v>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KT Corporation</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KT</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>14.09000015258789</v>
+      </c>
+      <c r="D20">
+        <v>15.60999965667725</v>
+      </c>
+      <c r="E20">
+        <v>14.22000026702881</v>
+      </c>
+      <c r="F20">
+        <v>11.60000038146973</v>
+      </c>
+      <c r="G20">
+        <v>11.01000022888184</v>
+      </c>
+      <c r="H20">
+        <v>12.56999969482422</v>
+      </c>
+      <c r="I20">
+        <v>13.5</v>
+      </c>
+      <c r="J20">
+        <v>13.4399995803833</v>
+      </c>
+      <c r="K20">
+        <v>15.52000045776367</v>
+      </c>
+      <c r="L20">
+        <v>18.96999931335449</v>
+      </c>
+      <c r="M20">
+        <v>21.69000053405762</v>
+      </c>
+      <c r="T20">
+        <v>0.729</v>
+      </c>
+      <c r="U20">
+        <v>0.711</v>
+      </c>
+      <c r="V20">
+        <v>0.5429999999999999</v>
+      </c>
+      <c r="W20">
+        <v>0.6</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="Z20">
+        <v>0.6457499999999999</v>
+      </c>
+      <c r="AA20">
+        <v>2.583</v>
+      </c>
+      <c r="AB20">
+        <v>14.09000015258789</v>
+      </c>
+      <c r="AC20">
+        <v>21.69000053405762</v>
+      </c>
+      <c r="AD20">
+        <v>7.600000381469727</v>
+      </c>
+      <c r="AE20">
+        <v>10.18300038146973</v>
+      </c>
+      <c r="AF20">
+        <v>1.018300038146973</v>
+      </c>
+      <c r="AG20">
+        <v>24</v>
+      </c>
+      <c r="AH20">
+        <v>520.5600128173828</v>
+      </c>
+      <c r="AI20">
+        <v>5.091500190734863</v>
+      </c>
+      <c r="AJ20">
+        <v>3.22875</v>
+      </c>
+      <c r="AK20">
+        <v>8.320250190734864</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Informa Plc</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>IFJPY</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="D21">
+        <v>19.65999984741211</v>
+      </c>
+      <c r="E21">
+        <v>16.1299991607666</v>
+      </c>
+      <c r="F21">
+        <v>23.07999992370605</v>
+      </c>
+      <c r="G21">
+        <v>14.97000026702881</v>
+      </c>
+      <c r="H21">
+        <v>14.15999984741211</v>
+      </c>
+      <c r="I21">
+        <v>15.01000022888184</v>
+      </c>
+      <c r="J21">
+        <v>20.05999946594238</v>
+      </c>
+      <c r="K21">
+        <v>20.14999961853027</v>
+      </c>
+      <c r="L21">
+        <v>24.09000015258789</v>
+      </c>
+      <c r="M21">
+        <v>21.72999954223633</v>
+      </c>
+      <c r="N21">
+        <v>1.845</v>
+      </c>
+      <c r="O21">
+        <v>0.494</v>
+      </c>
+      <c r="P21">
+        <v>0.5720000000000001</v>
+      </c>
+      <c r="Q21">
+        <v>0.579</v>
+      </c>
+      <c r="T21">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="U21">
+        <v>0.32</v>
+      </c>
+      <c r="V21">
+        <v>0.473</v>
+      </c>
+      <c r="W21">
+        <v>0.5389999999999999</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>media</t>
+        </is>
+      </c>
+      <c r="Z21">
+        <v>0.61175</v>
+      </c>
+      <c r="AA21">
+        <v>4.894</v>
+      </c>
+      <c r="AB21">
+        <v>16.79999923706055</v>
+      </c>
+      <c r="AC21">
+        <v>21.72999954223633</v>
+      </c>
+      <c r="AD21">
+        <v>4.930000305175781</v>
+      </c>
+      <c r="AE21">
+        <v>9.824000305175781</v>
+      </c>
+      <c r="AF21">
+        <v>0.9824000305175782</v>
+      </c>
+      <c r="AG21">
+        <v>24</v>
+      </c>
+      <c r="AH21">
+        <v>521.5199890136719</v>
+      </c>
+      <c r="AI21">
+        <v>4.912000152587891</v>
+      </c>
+      <c r="AJ21">
+        <v>3.05875</v>
+      </c>
+      <c r="AK21">
+        <v>7.970750152587891</v>
+      </c>
+      <c r="AL21" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
